--- a/output/pdf_financials_xlsx/CSG.xlsx
+++ b/output/pdf_financials_xlsx/CSG.xlsx
@@ -4989,16 +4989,16 @@
         <v>-0.710838</v>
       </c>
       <c r="K91" s="3" t="n">
-        <v>0</v>
+        <v>-0.708448</v>
       </c>
       <c r="L91" s="3" t="n">
-        <v>0</v>
+        <v>-0.721261</v>
       </c>
       <c r="M91" s="3" t="n">
-        <v>0</v>
+        <v>-0.7277749999999999</v>
       </c>
       <c r="N91" s="3" t="n">
-        <v>0</v>
+        <v>-0.712282</v>
       </c>
     </row>
     <row r="92">
@@ -5014,16 +5014,16 @@
         <v>0.5587530000000001</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>1.330192</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>1.330192</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>2.627977</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>2.724019</v>
       </c>
       <c r="H92" s="1" t="inlineStr">
         <is>
@@ -5031,22 +5031,22 @@
         </is>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>2.724019</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>2.724019</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>2.724019</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>2.872117</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>2.872117</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>2.872117</v>
       </c>
     </row>
     <row r="93">
@@ -8260,7 +8260,11 @@
           <t>Share-based Payment Reserve</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
           <t>-</t>
@@ -8333,7 +8337,11 @@
           <t>Foreign Currency Translation Reserve</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>GainsLossesNotAffectingRetainedEarnings</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
           <t>-</t>
@@ -11513,7 +11521,11 @@
           <t>Share-based Payments Reserve</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr"/>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E54" t="inlineStr">
         <is>
           <t>-</t>
@@ -13281,7 +13293,11 @@
           <t>Share-based Payments Reserve</t>
         </is>
       </c>
-      <c r="D76" t="inlineStr"/>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E76" t="inlineStr">
         <is>
           <t>-</t>
@@ -15142,7 +15158,11 @@
           <t>Share-based Payments Reserve 1,330,192</t>
         </is>
       </c>
-      <c r="D99" t="inlineStr"/>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E99" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/CSG.xlsx
+++ b/output/pdf_financials_xlsx/CSG.xlsx
@@ -996,10 +996,10 @@
         </is>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>5.6e-05</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>9.3e-05</v>
       </c>
       <c r="K12" s="3" t="n">
         <v>0</v>
@@ -1828,10 +1828,10 @@
         </is>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-0.133977</v>
+        <v>-0.134033</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-0.096067</v>
+        <v>-0.09616</v>
       </c>
       <c r="K27" s="3" t="n">
         <v>-0.128842</v>
@@ -1932,10 +1932,10 @@
         </is>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-0.133977</v>
+        <v>-0.134033</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-0.096067</v>
+        <v>-0.09616</v>
       </c>
       <c r="K29" s="3" t="n">
         <v>-0.128842</v>
@@ -2166,16 +2166,16 @@
         <v>0.295796</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.002438</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>3.534608</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>1.46455</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.224439</v>
       </c>
       <c r="H34" s="1" t="inlineStr">
         <is>
@@ -2183,22 +2183,22 @@
         </is>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.056213</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.017837</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.009866</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.220927</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.186009</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>0.027162</v>
       </c>
     </row>
     <row r="35">
@@ -2262,16 +2262,16 @@
         <v>0.295796</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.002438</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>3.534608</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>1.46455</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.224439</v>
       </c>
       <c r="H36" s="1" t="inlineStr">
         <is>
@@ -2279,22 +2279,22 @@
         </is>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.056213</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.017837</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.009866</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.220927</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>0.186009</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>0.027162</v>
       </c>
     </row>
     <row r="37">
@@ -2838,16 +2838,16 @@
         <v>0</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.269606</v>
+        <v>0.267168</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>3.703635</v>
+        <v>0.169027</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>1.632088</v>
+        <v>0.167538</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.305846</v>
+        <v>0.08140699999999999</v>
       </c>
       <c r="H48" s="1" t="inlineStr">
         <is>
@@ -2855,22 +2855,22 @@
         </is>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.07706300000000001</v>
+        <v>0.02085</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.028256</v>
+        <v>0.010419</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.009866</v>
+        <v>0</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.222798</v>
+        <v>0.001871</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0.188612</v>
+        <v>0.002603</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>0.032596</v>
+        <v>0.005434</v>
       </c>
     </row>
     <row r="49">
@@ -7423,7 +7423,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -12327,7 +12327,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -13935,7 +13935,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -15476,7 +15476,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -25886,7 +25886,7 @@
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E233" t="inlineStr">

--- a/output/pdf_financials_xlsx/CSG.xlsx
+++ b/output/pdf_financials_xlsx/CSG.xlsx
@@ -540,15 +540,11 @@
           <t>Revenue</t>
         </is>
       </c>
-      <c r="B4" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C4" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D4" s="3" t="n">
         <v>0</v>
@@ -598,15 +594,11 @@
           <t xml:space="preserve">  Cost of Goods Sold</t>
         </is>
       </c>
-      <c r="B5" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C5" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D5" s="3" t="n">
         <v>0</v>
@@ -650,15 +642,11 @@
           <t>Gross Profit</t>
         </is>
       </c>
-      <c r="B6" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C6" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D6" s="3" t="n">
         <v>0</v>
@@ -708,15 +696,11 @@
           <t xml:space="preserve">  Selling, General, &amp; Admin. Expense</t>
         </is>
       </c>
-      <c r="B7" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C7" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B7" s="3" t="n">
+        <v>0.037163</v>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>0.04141</v>
       </c>
       <c r="D7" s="3" t="n">
         <v>0.016685</v>
@@ -760,15 +744,11 @@
           <t xml:space="preserve">  Research &amp; Development</t>
         </is>
       </c>
-      <c r="B8" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C8" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D8" s="3" t="n">
         <v>0</v>
@@ -812,18 +792,14 @@
           <t xml:space="preserve">  Other Operating Expense</t>
         </is>
       </c>
-      <c r="B9" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C9" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B9" s="3" t="n">
+        <v>0.019162</v>
+      </c>
+      <c r="C9" s="3" t="n">
+        <v>0.019037</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>0</v>
+        <v>0.029687</v>
       </c>
       <c r="E9" s="3" t="n">
         <v>0</v>
@@ -864,18 +840,14 @@
           <t xml:space="preserve">  Total Operating Expense</t>
         </is>
       </c>
-      <c r="B10" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C10" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B10" s="3" t="n">
+        <v>0.132435</v>
+      </c>
+      <c r="C10" s="3" t="n">
+        <v>0.002505</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0.016685</v>
+        <v>0.38741</v>
       </c>
       <c r="E10" s="3" t="n">
         <v>0.09114999999999999</v>
@@ -916,18 +888,14 @@
           <t>Operating Income</t>
         </is>
       </c>
-      <c r="B11" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C11" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B11" s="3" t="n">
+        <v>-0.132435</v>
+      </c>
+      <c r="C11" s="3" t="n">
+        <v>-0.002505</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>-0.016685</v>
+        <v>-0.38741</v>
       </c>
       <c r="E11" s="3" t="n">
         <v>-0.09114999999999999</v>
@@ -968,18 +936,14 @@
           <t xml:space="preserve">    Interest Income</t>
         </is>
       </c>
-      <c r="B12" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C12" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B12" s="3" t="n">
+        <v>-0.007441</v>
+      </c>
+      <c r="C12" s="3" t="n">
+        <v>-0.002065</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>-1e-05</v>
       </c>
       <c r="E12" s="3" t="n">
         <v>0</v>
@@ -1020,15 +984,11 @@
           <t xml:space="preserve">    Interest Expense</t>
         </is>
       </c>
-      <c r="B13" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C13" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B13" s="3" t="n">
+        <v>-0</v>
+      </c>
+      <c r="C13" s="3" t="n">
+        <v>-0</v>
       </c>
       <c r="D13" s="3" t="n">
         <v>-0</v>
@@ -1072,15 +1032,11 @@
           <t xml:space="preserve">  Net Interest Income</t>
         </is>
       </c>
-      <c r="B14" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C14" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D14" s="3" t="n">
         <v>0</v>
@@ -1124,18 +1080,14 @@
           <t xml:space="preserve">  Other Income (Expense)</t>
         </is>
       </c>
-      <c r="B15" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C15" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" s="3" t="n">
+        <v>7.499999999999999e-05</v>
       </c>
       <c r="D15" s="3" t="n">
-        <v>0</v>
+        <v>-0.00116</v>
       </c>
       <c r="E15" s="3" t="n">
         <v>0</v>
@@ -1176,15 +1128,11 @@
           <t>Pretax Income</t>
         </is>
       </c>
-      <c r="B16" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C16" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B16" s="3" t="n">
+        <v>-0.118876</v>
+      </c>
+      <c r="C16" s="3" t="n">
+        <v>-0.151934</v>
       </c>
       <c r="D16" s="3" t="n">
         <v>-1.504812</v>
@@ -1228,15 +1176,11 @@
           <t xml:space="preserve">  Tax Provision</t>
         </is>
       </c>
-      <c r="B17" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C17" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B17" s="3" t="n">
+        <v>-0</v>
+      </c>
+      <c r="C17" s="3" t="n">
+        <v>-0</v>
       </c>
       <c r="D17" s="3" t="n">
         <v>-0</v>
@@ -1424,15 +1368,11 @@
           <t xml:space="preserve">    Net Income (Continuing Operations)</t>
         </is>
       </c>
-      <c r="B20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B20" s="3" t="n">
+        <v>-0.118876</v>
+      </c>
+      <c r="C20" s="3" t="n">
+        <v>-0.151934</v>
       </c>
       <c r="D20" s="3" t="n">
         <v>-1.504812</v>
@@ -1476,15 +1416,11 @@
           <t xml:space="preserve">    Net Income (Discontinued Operations)</t>
         </is>
       </c>
-      <c r="B21" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C21" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C21" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D21" s="3" t="n">
         <v>0</v>
@@ -1528,15 +1464,11 @@
           <t xml:space="preserve">  Other Income (Minority Interest)</t>
         </is>
       </c>
-      <c r="B22" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C22" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C22" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D22" s="3" t="n">
         <v>0</v>
@@ -1580,15 +1512,11 @@
           <t>Net Income</t>
         </is>
       </c>
-      <c r="B23" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C23" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B23" s="3" t="n">
+        <v>-0.118876</v>
+      </c>
+      <c r="C23" s="3" t="n">
+        <v>-0.151934</v>
       </c>
       <c r="D23" s="3" t="n">
         <v>-1.504812</v>
@@ -1800,18 +1728,14 @@
           <t>EBIT</t>
         </is>
       </c>
-      <c r="B27" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C27" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B27" s="3" t="n">
+        <v>-0.111435</v>
+      </c>
+      <c r="C27" s="3" t="n">
+        <v>-0.149869</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-1.504812</v>
+        <v>-1.504802</v>
       </c>
       <c r="E27" s="3" t="n">
         <v>-3.060595</v>
@@ -1852,15 +1776,11 @@
           <t xml:space="preserve">  Depreciation, Depletion and Amortization</t>
         </is>
       </c>
-      <c r="B28" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C28" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B28" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C28" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D28" s="3" t="n">
         <v>0.045488</v>
@@ -1904,18 +1824,14 @@
           <t>EBITDA</t>
         </is>
       </c>
-      <c r="B29" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C29" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B29" s="3" t="n">
+        <v>-0.111435</v>
+      </c>
+      <c r="C29" s="3" t="n">
+        <v>-0.149869</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-1.459324</v>
+        <v>-1.459314</v>
       </c>
       <c r="E29" s="3" t="n">
         <v>-3.032901</v>
@@ -2028,15 +1944,11 @@
           <t>Tax Rate %</t>
         </is>
       </c>
-      <c r="B31" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C31" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B31" s="3" t="n">
+        <v>-0</v>
+      </c>
+      <c r="C31" s="3" t="n">
+        <v>-0</v>
       </c>
       <c r="D31" s="3" t="n">
         <v>-0</v>
@@ -5308,15 +5220,11 @@
           <t xml:space="preserve">  Net Income From Continuing Operations</t>
         </is>
       </c>
-      <c r="B99" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C99" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B99" s="3" t="n">
+        <v>-0.118876</v>
+      </c>
+      <c r="C99" s="3" t="n">
+        <v>-0.151934</v>
       </c>
       <c r="D99" s="3" t="n">
         <v>-1.504812</v>
@@ -5360,15 +5268,11 @@
           <t xml:space="preserve">  Cash Flow Depreciation, Depletion and Amortization</t>
         </is>
       </c>
-      <c r="B100" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C100" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B100" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C100" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D100" s="3" t="n">
         <v>0</v>
@@ -5412,15 +5316,11 @@
           <t xml:space="preserve">    Change In Receivables</t>
         </is>
       </c>
-      <c r="B101" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C101" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B101" s="3" t="n">
+        <v>0.007267</v>
+      </c>
+      <c r="C101" s="3" t="n">
+        <v>7.499999999999999e-05</v>
       </c>
       <c r="D101" s="3" t="n">
         <v>-0.029527</v>
@@ -5464,15 +5364,11 @@
           <t xml:space="preserve">    Change In Inventory</t>
         </is>
       </c>
-      <c r="B102" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C102" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B102" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C102" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D102" s="3" t="n">
         <v>0</v>
@@ -5516,15 +5412,11 @@
           <t xml:space="preserve">    Change In Prepaid Assets</t>
         </is>
       </c>
-      <c r="B103" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C103" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B103" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C103" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D103" s="3" t="n">
         <v>0.161151</v>
@@ -5568,15 +5460,11 @@
           <t xml:space="preserve">    Change In Payables And Accrued Expense</t>
         </is>
       </c>
-      <c r="B104" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C104" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B104" s="3" t="n">
+        <v>-0.006872</v>
+      </c>
+      <c r="C104" s="3" t="n">
+        <v>0.003846</v>
       </c>
       <c r="D104" s="3" t="n">
         <v>-0.054208</v>
@@ -5620,15 +5508,11 @@
           <t xml:space="preserve">    Change In Other Working Capital</t>
         </is>
       </c>
-      <c r="B105" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C105" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B105" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C105" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D105" s="3" t="n">
         <v>0</v>
@@ -5672,18 +5556,14 @@
           <t xml:space="preserve">  Change In Working Capital</t>
         </is>
       </c>
-      <c r="B106" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C106" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B106" s="3" t="n">
+        <v>-0.11804</v>
+      </c>
+      <c r="C106" s="3" t="n">
+        <v>-0.148013</v>
       </c>
       <c r="D106" s="3" t="n">
-        <v>0.077416</v>
+        <v>-0.633929</v>
       </c>
       <c r="E106" s="3" t="n">
         <v>-0.118482</v>
@@ -5724,18 +5604,14 @@
           <t xml:space="preserve">  Stock Based Compensation</t>
         </is>
       </c>
-      <c r="B107" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C107" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B107" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C107" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D107" s="3" t="n">
-        <v>0</v>
+        <v>0.71292</v>
       </c>
       <c r="E107" s="3" t="n">
         <v>0</v>
@@ -5776,15 +5652,11 @@
           <t xml:space="preserve">  Asset Impairment Charge</t>
         </is>
       </c>
-      <c r="B108" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C108" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B108" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C108" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D108" s="3" t="n">
         <v>0</v>
@@ -5828,15 +5700,11 @@
           <t xml:space="preserve">  Cash from Discontinued Operating Activities</t>
         </is>
       </c>
-      <c r="B109" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C109" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B109" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C109" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D109" s="3" t="n">
         <v>0</v>
@@ -5880,15 +5748,11 @@
           <t xml:space="preserve">  Cash Flow from Others</t>
         </is>
       </c>
-      <c r="B110" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C110" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B110" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C110" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D110" s="3" t="n">
         <v>0</v>
@@ -5920,10 +5784,10 @@
         <v>0</v>
       </c>
       <c r="M110" s="3" t="n">
-        <v>0</v>
+        <v>0.010778</v>
       </c>
       <c r="N110" s="3" t="n">
-        <v>0</v>
+        <v>0.035197</v>
       </c>
     </row>
     <row r="111">
@@ -5932,27 +5796,23 @@
           <t xml:space="preserve">  Purchase Of Property, Plant, Equipment</t>
         </is>
       </c>
-      <c r="B111" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C111" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B111" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C111" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D111" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E111" s="3" t="n">
-        <v>0</v>
+        <v>-0.002841</v>
       </c>
       <c r="F111" s="3" t="n">
-        <v>0</v>
+        <v>-0.014816</v>
       </c>
       <c r="G111" s="3" t="n">
-        <v>0</v>
+        <v>-0.012254</v>
       </c>
       <c r="H111" s="1" t="inlineStr">
         <is>
@@ -5984,15 +5844,11 @@
           <t xml:space="preserve">  Sale Of Property, Plant, Equipment</t>
         </is>
       </c>
-      <c r="B112" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C112" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B112" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C112" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D112" s="3" t="n">
         <v>0</v>
@@ -6036,15 +5892,11 @@
           <t xml:space="preserve">  Purchase Of Business</t>
         </is>
       </c>
-      <c r="B113" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C113" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B113" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C113" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D113" s="3" t="n">
         <v>0</v>
@@ -6088,15 +5940,11 @@
           <t xml:space="preserve">  Purchase Of Investment</t>
         </is>
       </c>
-      <c r="B114" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C114" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B114" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C114" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D114" s="3" t="n">
         <v>0</v>
@@ -6140,15 +5988,11 @@
           <t xml:space="preserve">  Sale Of Investment</t>
         </is>
       </c>
-      <c r="B115" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C115" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B115" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C115" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D115" s="3" t="n">
         <v>0</v>
@@ -6192,15 +6036,11 @@
           <t xml:space="preserve">  Net Intangibles Purchase And Sale</t>
         </is>
       </c>
-      <c r="B116" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C116" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B116" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C116" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D116" s="3" t="n">
         <v>0</v>
@@ -6244,15 +6084,11 @@
           <t xml:space="preserve">  Cash From Discontinued Investing Activities</t>
         </is>
       </c>
-      <c r="B117" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C117" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B117" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C117" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D117" s="3" t="n">
         <v>0</v>
@@ -6296,15 +6132,11 @@
           <t xml:space="preserve">  Cash From Other Investing Activities</t>
         </is>
       </c>
-      <c r="B118" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C118" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B118" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C118" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D118" s="3" t="n">
         <v>0</v>
@@ -6420,15 +6252,11 @@
           <t xml:space="preserve">  Issuance of Stock</t>
         </is>
       </c>
-      <c r="B120" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C120" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B120" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C120" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D120" s="3" t="n">
         <v>0</v>
@@ -6472,15 +6300,11 @@
           <t xml:space="preserve">  Repurchase of Stock</t>
         </is>
       </c>
-      <c r="B121" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C121" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B121" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C121" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D121" s="3" t="n">
         <v>0</v>
@@ -6524,15 +6348,11 @@
           <t xml:space="preserve">  Net Issuance of Preferred Stock</t>
         </is>
       </c>
-      <c r="B122" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C122" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B122" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C122" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D122" s="3" t="n">
         <v>0</v>
@@ -6576,15 +6396,11 @@
           <t xml:space="preserve">    Issuance of Debt</t>
         </is>
       </c>
-      <c r="B123" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C123" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B123" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C123" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D123" s="3" t="n">
         <v>0</v>
@@ -6628,15 +6444,11 @@
           <t xml:space="preserve">    Payments of Debt</t>
         </is>
       </c>
-      <c r="B124" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C124" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B124" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C124" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D124" s="3" t="n">
         <v>0</v>
@@ -6680,15 +6492,11 @@
           <t xml:space="preserve">  Net Issuance of Debt</t>
         </is>
       </c>
-      <c r="B125" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C125" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B125" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C125" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D125" s="3" t="n">
         <v>0</v>
@@ -6732,15 +6540,11 @@
           <t xml:space="preserve">  Cash Flow for Dividends</t>
         </is>
       </c>
-      <c r="B126" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C126" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B126" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C126" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D126" s="3" t="n">
         <v>0</v>
@@ -6856,15 +6660,11 @@
           <t xml:space="preserve">  Other Financing</t>
         </is>
       </c>
-      <c r="B128" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C128" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B128" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C128" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D128" s="3" t="n">
         <v>0</v>
@@ -6977,10 +6777,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C130" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C130" s="3" t="n">
+        <v>0.168809</v>
       </c>
       <c r="D130" s="3" t="n">
         <v>0.002438</v>
@@ -7024,15 +6822,11 @@
           <t xml:space="preserve">    Effect of Exchange Rate Changes</t>
         </is>
       </c>
-      <c r="B131" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C131" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B131" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C131" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D131" s="3" t="n">
         <v>0</v>
@@ -7076,15 +6870,11 @@
           <t xml:space="preserve">  Net Change in Cash</t>
         </is>
       </c>
-      <c r="B132" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C132" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B132" s="3" t="n">
+        <v>-0.118481</v>
+      </c>
+      <c r="C132" s="3" t="n">
+        <v>0.126987</v>
       </c>
       <c r="D132" s="3" t="n">
         <v>0.142876</v>
@@ -7133,10 +6923,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C133" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C133" s="3" t="n">
+        <v>0.295796</v>
       </c>
       <c r="D133" s="3" t="n">
         <v>0.145314</v>
@@ -7180,27 +6968,23 @@
           <t>Capital Expenditure</t>
         </is>
       </c>
-      <c r="B134" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C134" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B134" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C134" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D134" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E134" s="3" t="n">
-        <v>0</v>
+        <v>-0.002841</v>
       </c>
       <c r="F134" s="3" t="n">
-        <v>0</v>
+        <v>-0.014816</v>
       </c>
       <c r="G134" s="3" t="n">
-        <v>0</v>
+        <v>-0.012254</v>
       </c>
       <c r="H134" s="1" t="inlineStr">
         <is>
@@ -7309,7 +7093,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q272"/>
+  <dimension ref="A1:Q319"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -17736,7 +17520,11 @@
           <t>Accretion Expense 5,6</t>
         </is>
       </c>
-      <c r="D131" t="inlineStr"/>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E131" t="inlineStr">
         <is>
           <t>-</t>
@@ -22133,7 +21921,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D186" t="inlineStr"/>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E186" t="inlineStr">
         <is>
           <t>-</t>
@@ -22289,7 +22081,11 @@
           <t>Shares issued for cash</t>
         </is>
       </c>
-      <c r="D188" t="inlineStr"/>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E188" t="inlineStr">
         <is>
           <t>-</t>
@@ -23504,7 +23300,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D203" t="inlineStr"/>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E203" t="inlineStr">
         <is>
           <t>-</t>
@@ -23902,34 +23702,32 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>OPERATING ACTIVITIES</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Accounting, Audit and Legal</t>
-        </is>
-      </c>
-      <c r="D208" t="inlineStr"/>
-      <c r="E208" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F208" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G208" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>NET LOSS FOR THE YEAR $</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
+      <c r="E208" s="5" t="n">
+        <v>-0.118876</v>
+      </c>
+      <c r="F208" s="5" t="n">
+        <v>-0.151934</v>
+      </c>
+      <c r="G208" s="5" t="n">
+        <v>-1.342595</v>
       </c>
       <c r="H208" t="inlineStr">
         <is>
@@ -23951,42 +23749,58 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L208" s="5" t="n">
-        <v>0.044941</v>
-      </c>
-      <c r="M208" s="5" t="n">
-        <v>0.02275</v>
-      </c>
-      <c r="N208" s="5" t="n">
-        <v>0.047408</v>
-      </c>
-      <c r="O208" s="5" t="n">
-        <v>0.0348</v>
-      </c>
-      <c r="P208" s="5" t="n">
-        <v>0.046801</v>
-      </c>
-      <c r="Q208" s="5" t="n">
-        <v>0.062928</v>
+      <c r="L208" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M208" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N208" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O208" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P208" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q208" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>ITEM NOT REQUIRING AN OUTLAY OF CASH</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Accretion Expense 5,6</t>
-        </is>
-      </c>
-      <c r="D209" t="inlineStr"/>
+          <t>STOCK-BASED COMPENSATION</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E209" t="inlineStr">
         <is>
           <t>-</t>
@@ -23997,10 +23811,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G209" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G209" s="5" t="n">
+        <v>0.71292</v>
       </c>
       <c r="H209" t="inlineStr">
         <is>
@@ -24042,44 +23854,42 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P209" s="5" t="n">
-        <v>0.010778</v>
-      </c>
-      <c r="Q209" s="5" t="n">
-        <v>0.035197</v>
+      <c r="P209" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q209" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>ITEM NOT REQUIRING AN OUTLAY OF CASH</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Exploration and Evaluation Expenditures 4</t>
+          <t>ITEM NOT REQUIRING AN OUTLAY OF CASH total</t>
         </is>
       </c>
       <c r="D210" t="inlineStr"/>
-      <c r="E210" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F210" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G210" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E210" s="5" t="n">
+        <v>-0.132435</v>
+      </c>
+      <c r="F210" s="5" t="n">
+        <v>-0.151934</v>
+      </c>
+      <c r="G210" s="5" t="n">
+        <v>-0.629675</v>
       </c>
       <c r="H210" t="inlineStr">
         <is>
@@ -24101,60 +23911,66 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L210" s="5" t="n">
-        <v>0.002176</v>
-      </c>
-      <c r="M210" s="5" t="n">
-        <v>0.002074</v>
-      </c>
-      <c r="N210" s="5" t="n">
-        <v>0.003536</v>
-      </c>
-      <c r="O210" s="5" t="n">
-        <v>0.027154</v>
-      </c>
-      <c r="P210" s="5" t="n">
-        <v>0.188999</v>
-      </c>
-      <c r="Q210" s="5" t="n">
-        <v>0.21882</v>
+      <c r="L210" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M210" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N210" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O210" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P210" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q210" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>CHANGE IN NON-CASH WORKING CAPITAL ITEMS</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Management Fees 6</t>
+          <t>RECEIVABLES</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
-      <c r="E211" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F211" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G211" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
+      <c r="E211" s="5" t="n">
+        <v>0.007267</v>
+      </c>
+      <c r="F211" s="5" t="n">
+        <v>7.499999999999999e-05</v>
+      </c>
+      <c r="G211" s="5" t="n">
+        <v>-0.01076</v>
       </c>
       <c r="H211" t="inlineStr">
         <is>
@@ -24176,60 +23992,66 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L211" s="5" t="n">
-        <v>0.065014</v>
-      </c>
-      <c r="M211" s="5" t="n">
-        <v>0.085687</v>
-      </c>
-      <c r="N211" s="5" t="n">
-        <v>0.060455</v>
-      </c>
-      <c r="O211" s="5" t="n">
-        <v>0.266163</v>
-      </c>
-      <c r="P211" s="5" t="n">
-        <v>0.060104</v>
-      </c>
-      <c r="Q211" s="5" t="n">
-        <v>0.221965</v>
+      <c r="L211" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M211" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N211" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O211" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P211" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q211" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>CHANGE IN NON-CASH WORKING CAPITAL ITEMS</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>ACCOUNTS PAYABLE AND ACCRUED LIABILITIES</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>OtherOperatingExpenses</t>
-        </is>
-      </c>
-      <c r="E212" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F212" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G212" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>ChangeInPayablesAndAccruedExpense</t>
+        </is>
+      </c>
+      <c r="E212" s="5" t="n">
+        <v>0.007128</v>
+      </c>
+      <c r="F212" s="5" t="n">
+        <v>0.003846</v>
+      </c>
+      <c r="G212" s="5" t="n">
+        <v>0.006506</v>
       </c>
       <c r="H212" t="inlineStr">
         <is>
@@ -24251,60 +24073,66 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L212" s="5" t="n">
-        <v>0.016397</v>
-      </c>
-      <c r="M212" s="5" t="n">
-        <v>0.0194</v>
-      </c>
-      <c r="N212" s="5" t="n">
-        <v>0.014165</v>
-      </c>
-      <c r="O212" s="5" t="n">
-        <v>0.004643</v>
-      </c>
-      <c r="P212" s="5" t="n">
-        <v>0.00096</v>
-      </c>
-      <c r="Q212" s="5" t="n">
-        <v>0.035023</v>
+      <c r="L212" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M212" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N212" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O212" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P212" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q212" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>CHANGE IN NON-CASH WORKING CAPITAL ITEMS</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Travel</t>
+          <t>CHANGE IN NON-CASH WORKING CAPITAL ITEMS total</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
-      <c r="E213" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F213" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G213" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>ChangeInWorkingCapital</t>
+        </is>
+      </c>
+      <c r="E213" s="5" t="n">
+        <v>-0.11804</v>
+      </c>
+      <c r="F213" s="5" t="n">
+        <v>-0.148013</v>
+      </c>
+      <c r="G213" s="5" t="n">
+        <v>-0.633929</v>
       </c>
       <c r="H213" t="inlineStr">
         <is>
@@ -24326,60 +24154,64 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L213" s="5" t="n">
-        <v>0.003994</v>
-      </c>
-      <c r="M213" s="5" t="n">
-        <v>0.001927</v>
-      </c>
-      <c r="N213" s="5" t="n">
-        <v>0.002996</v>
-      </c>
-      <c r="O213" s="5" t="n">
-        <v>0.05007</v>
-      </c>
-      <c r="P213" s="5" t="n">
-        <v>0.020558</v>
-      </c>
-      <c r="Q213" s="5" t="n">
-        <v>0.034082</v>
+      <c r="L213" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M213" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N213" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O213" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P213" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q213" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>FINANCING ACTIVITY</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>LOSS BEFORE OTHER ITEM</t>
-        </is>
-      </c>
-      <c r="D214" t="inlineStr">
-        <is>
-          <t>OperatingIncome</t>
-        </is>
-      </c>
+          <t>SHARE CAPITAL ISSUED FOR CASH, NET</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr"/>
       <c r="E214" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F214" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G214" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F214" s="5" t="n">
+        <v>0.275</v>
+      </c>
+      <c r="G214" s="5" t="n">
+        <v>1.585774</v>
       </c>
       <c r="H214" t="inlineStr">
         <is>
@@ -24416,47 +24248,53 @@
           <t>-</t>
         </is>
       </c>
-      <c r="O214" s="5" t="n">
-        <v>-0.38283</v>
-      </c>
-      <c r="P214" s="5" t="n">
-        <v>-0.3282</v>
-      </c>
-      <c r="Q214" s="5" t="n">
-        <v>-0.608015</v>
+      <c r="O214" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P214" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q214" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>OTHER ITEM</t>
+          <t>FINANCING ACTIVITY</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Gain on Modification of Loans Payable and Dues to Related Parties 5,6</t>
-        </is>
-      </c>
-      <c r="D215" t="inlineStr"/>
+          <t>CHANGE IN CASH FOR THE YEAR</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>ChangesInCash</t>
+        </is>
+      </c>
       <c r="E215" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F215" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G215" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F215" s="5" t="n">
+        <v>0.126987</v>
+      </c>
+      <c r="G215" s="5" t="n">
+        <v>0.9518450000000001</v>
       </c>
       <c r="H215" t="inlineStr">
         <is>
@@ -24498,32 +24336,36 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P215" s="5" t="n">
-        <v>0.050389</v>
-      </c>
-      <c r="Q215" s="5" t="n">
-        <v>0.018478</v>
+      <c r="P215" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q215" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>OTHER ITEM</t>
+          <t>FINANCING ACTIVITY</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>NET LOSS FOR THE YEAR</t>
+          <t>CASH BEGINNING OF THE YEAR</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>NetIncome</t>
+          <t>BeginningCashPosition</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">
@@ -24531,15 +24373,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F216" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G216" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F216" s="5" t="n">
+        <v>0.168809</v>
+      </c>
+      <c r="G216" s="5" t="n">
+        <v>0.295796</v>
       </c>
       <c r="H216" t="inlineStr">
         <is>
@@ -24576,47 +24414,53 @@
           <t>-</t>
         </is>
       </c>
-      <c r="O216" s="5" t="n">
-        <v>-0.38283</v>
-      </c>
-      <c r="P216" s="5" t="n">
-        <v>-0.277811</v>
-      </c>
-      <c r="Q216" s="5" t="n">
-        <v>-0.589537</v>
+      <c r="O216" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P216" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q216" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>OTHER COMPREHENSIVE LOSS</t>
+          <t>FINANCING ACTIVITY</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Foreign Currency Translation Gain (Loss)</t>
-        </is>
-      </c>
-      <c r="D217" t="inlineStr"/>
+          <t>CASH END OF THE YEAR $</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>EndCashPosition</t>
+        </is>
+      </c>
       <c r="E217" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F217" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G217" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F217" s="5" t="n">
+        <v>0.295796</v>
+      </c>
+      <c r="G217" s="5" t="n">
+        <v>1.247641</v>
       </c>
       <c r="H217" t="inlineStr">
         <is>
@@ -24658,34 +24502,34 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P217" s="5" t="n">
-        <v>-0.006514</v>
-      </c>
-      <c r="Q217" s="5" t="n">
-        <v>0.015493</v>
+      <c r="P217" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q217" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>OTHER COMPREHENSIVE LOSS</t>
+          <t>SUPPLEMENTAL INFORMATION</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>NET COMPREHENSIVE LOSS FOR THE YEAR</t>
-        </is>
-      </c>
-      <c r="D218" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>INTEREST PAID IN CASH DURING THE YEAR $</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr"/>
       <c r="E218" t="inlineStr">
         <is>
           <t>-</t>
@@ -24721,48 +24565,54 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L218" s="5" t="n">
-        <v>-0.129684</v>
-      </c>
-      <c r="M218" s="5" t="n">
-        <v>-0.084646</v>
-      </c>
-      <c r="N218" s="5" t="n">
-        <v>-0.126452</v>
+      <c r="L218" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M218" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N218" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O218" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="P218" s="5" t="n">
-        <v>-0.284325</v>
-      </c>
-      <c r="Q218" s="5" t="n">
-        <v>-0.574044</v>
+      <c r="P218" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q218" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>OTHER COMPREHENSIVE LOSS</t>
+          <t>SUPPLEMENTAL INFORMATION</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>BASIC AND DILUTED LOSS PER SHARE</t>
-        </is>
-      </c>
-      <c r="D219" t="inlineStr">
-        <is>
-          <t>BasicEPS</t>
-        </is>
-      </c>
+          <t>INCOME TAXES PAID IN CASH DURING THE YEAR $</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr"/>
       <c r="E219" t="inlineStr">
         <is>
           <t>-</t>
@@ -24798,57 +24648,59 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L219" s="5" t="n">
-        <v>-2e-09</v>
-      </c>
-      <c r="M219" s="5" t="n">
-        <v>-1e-09</v>
-      </c>
-      <c r="N219" s="5" t="n">
-        <v>-2e-09</v>
+      <c r="L219" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M219" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N219" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O219" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="P219" s="5" t="n">
-        <v>-3e-09</v>
-      </c>
-      <c r="Q219" s="5" t="n">
-        <v>-6e-09</v>
+      <c r="P219" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q219" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>OTHER COMPREHENSIVE LOSS</t>
+          <t>ITEM NOT REQUIRING AN OUTLAY OF CASH</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>WEIGHTED AVERAGE NUMBER OF SHARES OUTSTANDING</t>
-        </is>
-      </c>
-      <c r="D220" t="inlineStr">
-        <is>
-          <t>BasicAverageShares</t>
-        </is>
-      </c>
-      <c r="E220" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F220" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>EXPLORATION COSTS WRITTEN OFF (RECOVERED)</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr"/>
+      <c r="E220" s="5" t="n">
+        <v>-0.013559</v>
+      </c>
+      <c r="F220" s="5" t="n">
+        <v>0.002505</v>
       </c>
       <c r="G220" t="inlineStr">
         <is>
@@ -24875,41 +24727,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L220" s="5" t="n">
-        <v>77.630523</v>
-      </c>
-      <c r="M220" s="5" t="n">
-        <v>80.351449</v>
-      </c>
-      <c r="N220" s="5" t="n">
-        <v>83.47251199999999</v>
+      <c r="L220" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M220" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N220" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O220" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="P220" s="5" t="n">
-        <v>90.07525200000001</v>
-      </c>
-      <c r="Q220" s="5" t="n">
-        <v>99.828676</v>
+      <c r="P220" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q220" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>OTHER ITEM</t>
+          <t>FINANCING ACTIVITIES</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Gain on Modification of Loans Payable and Dues to Related Parties 5</t>
+          <t>SHARE CAPITAL ISSUED FOR CASH</t>
         </is>
       </c>
       <c r="D221" t="inlineStr"/>
@@ -24918,10 +24780,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F221" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F221" s="5" t="n">
+        <v>0.275</v>
       </c>
       <c r="G221" t="inlineStr">
         <is>
@@ -24968,8 +24828,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P221" s="5" t="n">
-        <v>0.050389</v>
+      <c r="P221" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="Q221" t="inlineStr">
         <is>
@@ -24980,29 +24842,25 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>OTHER COMPREHEENSIVE LOSS</t>
+          <t>INVESTING ACTIVITIES</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Foreign Currency Translation Loss</t>
+          <t>EXPLORATION COSTS</t>
         </is>
       </c>
       <c r="D222" t="inlineStr"/>
-      <c r="E222" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F222" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E222" s="5" t="n">
+        <v>-0.000441</v>
+      </c>
+      <c r="F222" s="5" t="n">
+        <v>-0.002505</v>
       </c>
       <c r="G222" t="inlineStr">
         <is>
@@ -25044,11 +24902,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="O222" s="5" t="n">
-        <v>-0.012813</v>
-      </c>
-      <c r="P222" s="5" t="n">
-        <v>-0.006514</v>
+      <c r="O222" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P222" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="Q222" t="inlineStr">
         <is>
@@ -25059,33 +24921,29 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>OTHER COMPREHEENSIVE LOSS</t>
+          <t>INVESTING ACTIVITIES</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>NET COMPREHENSIVE LOSS FOR THE YEAR</t>
+          <t>CHANGE IN CASH FOR THE YEAR</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
-      <c r="E223" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F223" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>ChangesInCash</t>
+        </is>
+      </c>
+      <c r="E223" s="5" t="n">
+        <v>-0.118481</v>
+      </c>
+      <c r="F223" s="5" t="n">
+        <v>0.126987</v>
       </c>
       <c r="G223" t="inlineStr">
         <is>
@@ -25127,11 +24985,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="O223" s="5" t="n">
-        <v>-0.395643</v>
-      </c>
-      <c r="P223" s="5" t="n">
-        <v>-0.284325</v>
+      <c r="O223" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P223" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="Q223" t="inlineStr">
         <is>
@@ -25142,33 +25004,25 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>OTHER COMPREHEENSIVE LOSS</t>
+          <t>CASH AND CASH EQUIVALENTS</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>BASIC AND DILUTED LOSS PER SHARE</t>
-        </is>
-      </c>
-      <c r="D224" t="inlineStr">
-        <is>
-          <t>BasicEPS</t>
-        </is>
-      </c>
-      <c r="E224" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F224" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>BEGINNING OF THE YEAR</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr"/>
+      <c r="E224" s="5" t="n">
+        <v>0.28729</v>
+      </c>
+      <c r="F224" s="5" t="n">
+        <v>0.168809</v>
       </c>
       <c r="G224" t="inlineStr">
         <is>
@@ -25210,11 +25064,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="O224" s="5" t="n">
-        <v>-5e-09</v>
-      </c>
-      <c r="P224" s="5" t="n">
-        <v>-3e-09</v>
+      <c r="O224" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P224" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="Q224" t="inlineStr">
         <is>
@@ -25225,33 +25083,25 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>OTHER COMPREHEENSIVE LOSS</t>
+          <t>CASH AND CASH EQUIVALENTS</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>WEIGHTED AVERAGE NUMBER OF SHARES OUTSTANDING</t>
-        </is>
-      </c>
-      <c r="D225" t="inlineStr">
-        <is>
-          <t>BasicAverageShares</t>
-        </is>
-      </c>
-      <c r="E225" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F225" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>END OF THE YEAR $</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr"/>
+      <c r="E225" s="5" t="n">
+        <v>0.168809</v>
+      </c>
+      <c r="F225" s="5" t="n">
+        <v>0.295796</v>
       </c>
       <c r="G225" t="inlineStr">
         <is>
@@ -25293,11 +25143,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="O225" s="5" t="n">
-        <v>90.07525200000001</v>
-      </c>
-      <c r="P225" s="5" t="n">
-        <v>90.07525200000001</v>
+      <c r="O225" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P225" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="Q225" t="inlineStr">
         <is>
@@ -25308,29 +25162,25 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>CASH AND CASH EQUIVALENTS CONSIST OF</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Telecommunications</t>
+          <t>CASH $</t>
         </is>
       </c>
       <c r="D226" t="inlineStr"/>
-      <c r="E226" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F226" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E226" s="5" t="n">
+        <v>0.038809</v>
+      </c>
+      <c r="F226" s="5" t="n">
+        <v>0.295796</v>
       </c>
       <c r="G226" t="inlineStr">
         <is>
@@ -25357,17 +25207,25 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L226" s="5" t="n">
-        <v>0.001511</v>
-      </c>
-      <c r="M226" s="5" t="n">
-        <v>0.000661</v>
-      </c>
-      <c r="N226" s="5" t="n">
-        <v>0.000282</v>
-      </c>
-      <c r="O226" s="5" t="n">
-        <v>0.000758</v>
+      <c r="L226" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M226" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N226" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O226" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="P226" t="inlineStr">
         <is>
@@ -25383,28 +25241,22 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>CASH AND CASH EQUIVALENTS CONSIST OF</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>NET LOSS FOR THE YEAR</t>
-        </is>
-      </c>
-      <c r="D227" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
-      <c r="E227" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>TERM DEPOSIT</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr"/>
+      <c r="E227" s="5" t="n">
+        <v>0.13</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -25436,17 +25288,25 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L227" s="5" t="n">
-        <v>-0.133977</v>
-      </c>
-      <c r="M227" s="5" t="n">
-        <v>-0.096067</v>
-      </c>
-      <c r="N227" s="5" t="n">
-        <v>-0.128842</v>
-      </c>
-      <c r="O227" s="5" t="n">
-        <v>-0.38283</v>
+      <c r="L227" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M227" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N227" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O227" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="P227" t="inlineStr">
         <is>
@@ -25462,29 +25322,25 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>OTHER COMPREHENSIVE GAIN (LOSS)</t>
+          <t>CASH AND CASH EQUIVALENTS CONSIST OF</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Foreign Currency Translation Gain (Loss)</t>
+          <t>CASH AND CASH EQUIVALENTS CONSIST OF total</t>
         </is>
       </c>
       <c r="D228" t="inlineStr"/>
-      <c r="E228" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F228" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E228" s="5" t="n">
+        <v>0.168809</v>
+      </c>
+      <c r="F228" s="5" t="n">
+        <v>0.295796</v>
       </c>
       <c r="G228" t="inlineStr">
         <is>
@@ -25521,11 +25377,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N228" s="5" t="n">
-        <v>0.00239</v>
-      </c>
-      <c r="O228" s="5" t="n">
-        <v>-0.012813</v>
+      <c r="N228" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O228" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="P228" t="inlineStr">
         <is>
@@ -25541,24 +25401,20 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>OTHER COMPREHENSIVE GAIN (LOSS)</t>
+          <t>CASH AND CASH EQUIVALENTS CONSIST OF</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>NET COMPREHENSIVE LOSS FOR THE YEAR</t>
-        </is>
-      </c>
-      <c r="D229" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>INTEREST PAID IN CASH DURING THE YEAR $</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr"/>
       <c r="E229" t="inlineStr">
         <is>
           <t>-</t>
@@ -25604,11 +25460,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N229" s="5" t="n">
-        <v>-0.126452</v>
-      </c>
-      <c r="O229" s="5" t="n">
-        <v>-0.395643</v>
+      <c r="N229" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O229" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="P229" t="inlineStr">
         <is>
@@ -25624,24 +25484,20 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>OTHER COMPREHENSIVE GAIN (LOSS)</t>
+          <t>CASH AND CASH EQUIVALENTS CONSIST OF</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>BASIC AND DILUTED LOSS PER SHARE</t>
-        </is>
-      </c>
-      <c r="D230" t="inlineStr">
-        <is>
-          <t>BasicEPS</t>
-        </is>
-      </c>
+          <t>INCOME TAXES PAID IN CASH DURING THE YEAR $</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr"/>
       <c r="E230" t="inlineStr">
         <is>
           <t>-</t>
@@ -25687,11 +25543,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N230" s="5" t="n">
-        <v>-2e-09</v>
-      </c>
-      <c r="O230" s="5" t="n">
-        <v>-5e-09</v>
+      <c r="N230" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O230" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="P230" t="inlineStr">
         <is>
@@ -25707,28 +25567,26 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>OTHER COMPREHENSIVE GAIN (LOSS)</t>
+          <t>NON-CASH TRANSACTIONS</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>WEIGHTED AVERAGE NUMBER OF SHARES OUTSTANDING</t>
+          <t>ACCRUED EXPLORATION COSTS - ACCOUNTS PAYABLE $</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>BasicAverageShares</t>
-        </is>
-      </c>
-      <c r="E231" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>ChangeInPayablesAndAccruedExpense</t>
+        </is>
+      </c>
+      <c r="E231" s="5" t="n">
+        <v>-0.014</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -25770,11 +25628,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N231" s="5" t="n">
-        <v>83.47251199999999</v>
-      </c>
-      <c r="O231" s="5" t="n">
-        <v>90.07525200000001</v>
+      <c r="N231" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O231" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="P231" t="inlineStr">
         <is>
@@ -25800,14 +25662,10 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>LOSS BEFORE OTHER ITEMS</t>
-        </is>
-      </c>
-      <c r="D232" t="inlineStr">
-        <is>
-          <t>OperatingIncome</t>
-        </is>
-      </c>
+          <t>Accounting, Audit and Legal</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr"/>
       <c r="E232" t="inlineStr">
         <is>
           <t>-</t>
@@ -25844,28 +25702,22 @@
         </is>
       </c>
       <c r="L232" s="5" t="n">
-        <v>-0.134033</v>
+        <v>0.044941</v>
       </c>
       <c r="M232" s="5" t="n">
-        <v>-0.132499</v>
+        <v>0.02275</v>
       </c>
       <c r="N232" s="5" t="n">
-        <v>-0.128842</v>
-      </c>
-      <c r="O232" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P232" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q232" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.047408</v>
+      </c>
+      <c r="O232" s="5" t="n">
+        <v>0.0348</v>
+      </c>
+      <c r="P232" s="5" t="n">
+        <v>0.046801</v>
+      </c>
+      <c r="Q232" s="5" t="n">
+        <v>0.062928</v>
       </c>
     </row>
     <row r="233">
@@ -25881,14 +25733,10 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Interest Income</t>
-        </is>
-      </c>
-      <c r="D233" t="inlineStr">
-        <is>
-          <t>InterestIncomeNonOperating</t>
-        </is>
-      </c>
+          <t>Accretion Expense 5,6</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr"/>
       <c r="E233" t="inlineStr">
         <is>
           <t>-</t>
@@ -25924,11 +25772,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L233" s="5" t="n">
-        <v>5.6e-05</v>
-      </c>
-      <c r="M233" s="5" t="n">
-        <v>9.3e-05</v>
+      <c r="L233" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M233" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="N233" t="inlineStr">
         <is>
@@ -25940,15 +25792,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P233" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q233" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="P233" s="5" t="n">
+        <v>0.010778</v>
+      </c>
+      <c r="Q233" s="5" t="n">
+        <v>0.035197</v>
       </c>
     </row>
     <row r="234">
@@ -25964,7 +25812,7 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Recovery of Colombia Sales Tax Receivable</t>
+          <t>Exploration and Evaluation Expenditures 4</t>
         </is>
       </c>
       <c r="D234" t="inlineStr"/>
@@ -26003,33 +25851,23 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L234" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L234" s="5" t="n">
+        <v>0.002176</v>
       </c>
       <c r="M234" s="5" t="n">
-        <v>0.036339</v>
-      </c>
-      <c r="N234" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O234" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P234" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q234" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.002074</v>
+      </c>
+      <c r="N234" s="5" t="n">
+        <v>0.003536</v>
+      </c>
+      <c r="O234" s="5" t="n">
+        <v>0.027154</v>
+      </c>
+      <c r="P234" s="5" t="n">
+        <v>0.188999</v>
+      </c>
+      <c r="Q234" s="5" t="n">
+        <v>0.21882</v>
       </c>
     </row>
     <row r="235">
@@ -26040,15 +25878,19 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>OTHER COMPREHENSIVE LOSS</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Foreign Currency Translation Gain</t>
-        </is>
-      </c>
-      <c r="D235" t="inlineStr"/>
+          <t>Management Fees 6</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E235" t="inlineStr">
         <is>
           <t>-</t>
@@ -26085,28 +25927,22 @@
         </is>
       </c>
       <c r="L235" s="5" t="n">
-        <v>0.004293</v>
+        <v>0.065014</v>
       </c>
       <c r="M235" s="5" t="n">
-        <v>0.011421</v>
+        <v>0.085687</v>
       </c>
       <c r="N235" s="5" t="n">
-        <v>0.00239</v>
-      </c>
-      <c r="O235" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P235" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q235" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.060455</v>
+      </c>
+      <c r="O235" s="5" t="n">
+        <v>0.266163</v>
+      </c>
+      <c r="P235" s="5" t="n">
+        <v>0.060104</v>
+      </c>
+      <c r="Q235" s="5" t="n">
+        <v>0.221965</v>
       </c>
     </row>
     <row r="236">
@@ -26122,10 +25958,14 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Recovery of Columbia Sales Tax Receivable</t>
-        </is>
-      </c>
-      <c r="D236" t="inlineStr"/>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
       <c r="E236" t="inlineStr">
         <is>
           <t>-</t>
@@ -26161,33 +26001,23 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L236" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L236" s="5" t="n">
+        <v>0.016397</v>
       </c>
       <c r="M236" s="5" t="n">
-        <v>0.036339</v>
-      </c>
-      <c r="N236" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O236" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P236" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q236" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.0194</v>
+      </c>
+      <c r="N236" s="5" t="n">
+        <v>0.014165</v>
+      </c>
+      <c r="O236" s="5" t="n">
+        <v>0.004643</v>
+      </c>
+      <c r="P236" s="5" t="n">
+        <v>0.00096</v>
+      </c>
+      <c r="Q236" s="5" t="n">
+        <v>0.035023</v>
       </c>
     </row>
     <row r="237">
@@ -26196,13 +26026,21 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B237" t="inlineStr"/>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Exploration Expenses (Note 4) $</t>
-        </is>
-      </c>
-      <c r="D237" t="inlineStr"/>
+          <t>Travel</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E237" t="inlineStr">
         <is>
           <t>-</t>
@@ -26223,46 +26061,38 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I237" s="5" t="n">
-        <v>1.754185</v>
-      </c>
-      <c r="J237" s="5" t="n">
-        <v>1.63686</v>
+      <c r="I237" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J237" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K237" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="L237" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M237" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N237" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O237" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P237" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q237" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L237" s="5" t="n">
+        <v>0.003994</v>
+      </c>
+      <c r="M237" s="5" t="n">
+        <v>0.001927</v>
+      </c>
+      <c r="N237" s="5" t="n">
+        <v>0.002996</v>
+      </c>
+      <c r="O237" s="5" t="n">
+        <v>0.05007</v>
+      </c>
+      <c r="P237" s="5" t="n">
+        <v>0.020558</v>
+      </c>
+      <c r="Q237" s="5" t="n">
+        <v>0.034082</v>
       </c>
     </row>
     <row r="238">
@@ -26273,15 +26103,19 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>General and Administrative Expenses</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Administrative fees and compensation (Note 6)</t>
-        </is>
-      </c>
-      <c r="D238" t="inlineStr"/>
+          <t>LOSS BEFORE OTHER ITEM</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>OperatingIncome</t>
+        </is>
+      </c>
       <c r="E238" t="inlineStr">
         <is>
           <t>-</t>
@@ -26302,11 +26136,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I238" s="5" t="n">
-        <v>0.299304</v>
-      </c>
-      <c r="J238" s="5" t="n">
-        <v>0.313142</v>
+      <c r="I238" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J238" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K238" t="inlineStr">
         <is>
@@ -26328,20 +26166,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="O238" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P238" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q238" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="O238" s="5" t="n">
+        <v>-0.38283</v>
+      </c>
+      <c r="P238" s="5" t="n">
+        <v>-0.3282</v>
+      </c>
+      <c r="Q238" s="5" t="n">
+        <v>-0.608015</v>
       </c>
     </row>
     <row r="239">
@@ -26352,19 +26184,15 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>General and Administrative Expenses</t>
+          <t>OTHER ITEM</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Depreciation</t>
-        </is>
-      </c>
-      <c r="D239" t="inlineStr">
-        <is>
-          <t>Depreciation</t>
-        </is>
-      </c>
+          <t>Gain on Modification of Loans Payable and Dues to Related Parties 5,6</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr"/>
       <c r="E239" t="inlineStr">
         <is>
           <t>-</t>
@@ -26380,14 +26208,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H239" s="5" t="n">
-        <v>0.027694</v>
-      </c>
-      <c r="I239" s="5" t="n">
-        <v>0.003542</v>
-      </c>
-      <c r="J239" s="5" t="n">
-        <v>0.005686</v>
+      <c r="H239" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I239" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J239" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K239" t="inlineStr">
         <is>
@@ -26414,15 +26248,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P239" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q239" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="P239" s="5" t="n">
+        <v>0.050389</v>
+      </c>
+      <c r="Q239" s="5" t="n">
+        <v>0.018478</v>
       </c>
     </row>
     <row r="240">
@@ -26433,17 +26263,17 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>General and Administrative Expenses</t>
+          <t>OTHER ITEM</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Foreign exchange</t>
+          <t>NET LOSS FOR THE YEAR</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>ForeignExchangeTradingGains</t>
+          <t>NetIncome</t>
         </is>
       </c>
       <c r="E240" t="inlineStr">
@@ -26461,14 +26291,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H240" s="5" t="n">
-        <v>-0.006906</v>
-      </c>
-      <c r="I240" s="5" t="n">
-        <v>0.01266</v>
-      </c>
-      <c r="J240" s="5" t="n">
-        <v>-0.007856</v>
+      <c r="H240" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I240" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J240" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K240" t="inlineStr">
         <is>
@@ -26490,20 +26326,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="O240" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P240" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q240" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="O240" s="5" t="n">
+        <v>-0.38283</v>
+      </c>
+      <c r="P240" s="5" t="n">
+        <v>-0.277811</v>
+      </c>
+      <c r="Q240" s="5" t="n">
+        <v>-0.589537</v>
       </c>
     </row>
     <row r="241">
@@ -26514,12 +26344,12 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>General and Administrative Expenses</t>
+          <t>OTHER COMPREHENSIVE LOSS</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Legal, accounting and audit</t>
+          <t>Foreign Currency Translation Gain (Loss)</t>
         </is>
       </c>
       <c r="D241" t="inlineStr"/>
@@ -26538,14 +26368,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H241" s="5" t="n">
-        <v>0.48218</v>
-      </c>
-      <c r="I241" s="5" t="n">
-        <v>0.348285</v>
-      </c>
-      <c r="J241" s="5" t="n">
-        <v>0.137853</v>
+      <c r="H241" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I241" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J241" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K241" t="inlineStr">
         <is>
@@ -26572,15 +26408,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P241" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q241" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="P241" s="5" t="n">
+        <v>-0.006514</v>
+      </c>
+      <c r="Q241" s="5" t="n">
+        <v>0.015493</v>
       </c>
     </row>
     <row r="242">
@@ -26591,15 +26423,19 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>General and Administrative Expenses</t>
+          <t>OTHER COMPREHENSIVE LOSS</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Office and sundry</t>
-        </is>
-      </c>
-      <c r="D242" t="inlineStr"/>
+          <t>NET COMPREHENSIVE LOSS FOR THE YEAR</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E242" t="inlineStr">
         <is>
           <t>-</t>
@@ -26615,49 +26451,45 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H242" s="5" t="n">
-        <v>0.178829</v>
-      </c>
-      <c r="I242" s="5" t="n">
-        <v>0.201335</v>
-      </c>
-      <c r="J242" s="5" t="n">
-        <v>0.185196</v>
+      <c r="H242" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I242" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J242" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K242" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="L242" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M242" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N242" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L242" s="5" t="n">
+        <v>-0.129684</v>
+      </c>
+      <c r="M242" s="5" t="n">
+        <v>-0.084646</v>
+      </c>
+      <c r="N242" s="5" t="n">
+        <v>-0.126452</v>
       </c>
       <c r="O242" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="P242" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q242" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="P242" s="5" t="n">
+        <v>-0.284325</v>
+      </c>
+      <c r="Q242" s="5" t="n">
+        <v>-0.574044</v>
       </c>
     </row>
     <row r="243">
@@ -26668,15 +26500,19 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>General and Administrative Expenses</t>
+          <t>OTHER COMPREHENSIVE LOSS</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Share-based compensation</t>
-        </is>
-      </c>
-      <c r="D243" t="inlineStr"/>
+          <t>BASIC AND DILUTED LOSS PER SHARE</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
       <c r="E243" t="inlineStr">
         <is>
           <t>-</t>
@@ -26697,46 +26533,40 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I243" s="5" t="n">
-        <v>0.643169</v>
-      </c>
-      <c r="J243" s="5" t="n">
-        <v>0.032109</v>
+      <c r="I243" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J243" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K243" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="L243" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M243" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N243" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L243" s="5" t="n">
+        <v>-2e-09</v>
+      </c>
+      <c r="M243" s="5" t="n">
+        <v>-1e-09</v>
+      </c>
+      <c r="N243" s="5" t="n">
+        <v>-2e-09</v>
       </c>
       <c r="O243" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="P243" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q243" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="P243" s="5" t="n">
+        <v>-3e-09</v>
+      </c>
+      <c r="Q243" s="5" t="n">
+        <v>-6e-09</v>
       </c>
     </row>
     <row r="244">
@@ -26747,15 +26577,19 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>General and Administrative Expenses</t>
+          <t>OTHER COMPREHENSIVE LOSS</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Telecommunications</t>
-        </is>
-      </c>
-      <c r="D244" t="inlineStr"/>
+          <t>WEIGHTED AVERAGE NUMBER OF SHARES OUTSTANDING</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>BasicAverageShares</t>
+        </is>
+      </c>
       <c r="E244" t="inlineStr">
         <is>
           <t>-</t>
@@ -26771,49 +26605,45 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H244" s="5" t="n">
-        <v>0.034108</v>
-      </c>
-      <c r="I244" s="5" t="n">
-        <v>0.027074</v>
-      </c>
-      <c r="J244" s="5" t="n">
-        <v>0.027959</v>
+      <c r="H244" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I244" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J244" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K244" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="L244" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M244" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N244" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L244" s="5" t="n">
+        <v>77.630523</v>
+      </c>
+      <c r="M244" s="5" t="n">
+        <v>80.351449</v>
+      </c>
+      <c r="N244" s="5" t="n">
+        <v>83.47251199999999</v>
       </c>
       <c r="O244" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="P244" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q244" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="P244" s="5" t="n">
+        <v>90.07525200000001</v>
+      </c>
+      <c r="Q244" s="5" t="n">
+        <v>99.828676</v>
       </c>
     </row>
     <row r="245">
@@ -26824,19 +26654,15 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>General and Administrative Expenses</t>
+          <t>OTHER ITEM</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Travel</t>
-        </is>
-      </c>
-      <c r="D245" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
+          <t>Gain on Modification of Loans Payable and Dues to Related Parties 5</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr"/>
       <c r="E245" t="inlineStr">
         <is>
           <t>-</t>
@@ -26852,14 +26678,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H245" s="5" t="n">
-        <v>0.09114999999999999</v>
-      </c>
-      <c r="I245" s="5" t="n">
-        <v>0.031644</v>
-      </c>
-      <c r="J245" s="5" t="n">
-        <v>0.1237</v>
+      <c r="H245" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I245" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J245" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K245" t="inlineStr">
         <is>
@@ -26886,10 +26718,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P245" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="P245" s="5" t="n">
+        <v>0.050389</v>
       </c>
       <c r="Q245" t="inlineStr">
         <is>
@@ -26905,19 +26735,15 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>General and Administrative Expenses</t>
+          <t>OTHER COMPREHEENSIVE LOSS</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Total General And Administrative Expenses</t>
-        </is>
-      </c>
-      <c r="D246" t="inlineStr">
-        <is>
-          <t>GeneralAndAdministrativeExpense</t>
-        </is>
-      </c>
+          <t>Foreign Currency Translation Loss</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr"/>
       <c r="E246" t="inlineStr">
         <is>
           <t>-</t>
@@ -26933,14 +26759,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H246" s="5" t="n">
-        <v>1.767952</v>
-      </c>
-      <c r="I246" s="5" t="n">
-        <v>1.567013</v>
-      </c>
-      <c r="J246" s="5" t="n">
-        <v>0.817789</v>
+      <c r="H246" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I246" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J246" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K246" t="inlineStr">
         <is>
@@ -26962,15 +26794,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="O246" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P246" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="O246" s="5" t="n">
+        <v>-0.012813</v>
+      </c>
+      <c r="P246" s="5" t="n">
+        <v>-0.006514</v>
       </c>
       <c r="Q246" t="inlineStr">
         <is>
@@ -26986,15 +26814,19 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>General and Administrative Expenses</t>
+          <t>OTHER COMPREHEENSIVE LOSS</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Net Loss Before Other Expenses</t>
-        </is>
-      </c>
-      <c r="D247" t="inlineStr"/>
+          <t>NET COMPREHENSIVE LOSS FOR THE YEAR</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E247" t="inlineStr">
         <is>
           <t>-</t>
@@ -27010,14 +26842,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H247" s="5" t="n">
-        <v>-2.953081</v>
-      </c>
-      <c r="I247" s="5" t="n">
-        <v>-3.321198</v>
-      </c>
-      <c r="J247" s="5" t="n">
-        <v>-2.454649</v>
+      <c r="H247" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I247" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J247" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K247" t="inlineStr">
         <is>
@@ -27039,15 +26877,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="O247" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P247" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="O247" s="5" t="n">
+        <v>-0.395643</v>
+      </c>
+      <c r="P247" s="5" t="n">
+        <v>-0.284325</v>
       </c>
       <c r="Q247" t="inlineStr">
         <is>
@@ -27063,17 +26897,17 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>General and Administrative Expenses</t>
+          <t>OTHER COMPREHEENSIVE LOSS</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Net Loss and Comprehensive Loss for the Year $</t>
+          <t>BASIC AND DILUTED LOSS PER SHARE</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>NetIncome</t>
+          <t>BasicEPS</t>
         </is>
       </c>
       <c r="E248" t="inlineStr">
@@ -27096,11 +26930,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I248" s="5" t="n">
-        <v>-3.321198</v>
-      </c>
-      <c r="J248" s="5" t="n">
-        <v>-2.454649</v>
+      <c r="I248" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J248" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K248" t="inlineStr">
         <is>
@@ -27122,15 +26960,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="O248" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P248" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="O248" s="5" t="n">
+        <v>-5e-09</v>
+      </c>
+      <c r="P248" s="5" t="n">
+        <v>-3e-09</v>
       </c>
       <c r="Q248" t="inlineStr">
         <is>
@@ -27146,17 +26980,17 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>General and Administrative Expenses</t>
+          <t>OTHER COMPREHEENSIVE LOSS</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Loss Per Share, Basic and diluted $</t>
+          <t>WEIGHTED AVERAGE NUMBER OF SHARES OUTSTANDING</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>BasicEPS</t>
+          <t>BasicAverageShares</t>
         </is>
       </c>
       <c r="E249" t="inlineStr">
@@ -27179,11 +27013,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I249" s="5" t="n">
-        <v>-5e-08</v>
-      </c>
-      <c r="J249" s="5" t="n">
-        <v>-3e-08</v>
+      <c r="I249" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J249" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K249" t="inlineStr">
         <is>
@@ -27205,15 +27043,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="O249" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P249" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="O249" s="5" t="n">
+        <v>90.07525200000001</v>
+      </c>
+      <c r="P249" s="5" t="n">
+        <v>90.07525200000001</v>
       </c>
       <c r="Q249" t="inlineStr">
         <is>
@@ -27229,12 +27063,12 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>Weighted Average Number of Shares Outstanding, Basic and</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Weighted Average Number of Shares Outstanding, Basic and diluted</t>
+          <t>Telecommunications</t>
         </is>
       </c>
       <c r="D250" t="inlineStr"/>
@@ -27248,42 +27082,42 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G250" s="5" t="n">
-        <v>31.509819</v>
-      </c>
-      <c r="H250" s="5" t="n">
-        <v>60.418467</v>
-      </c>
-      <c r="I250" s="5" t="n">
-        <v>72.793398</v>
-      </c>
-      <c r="J250" s="5" t="n">
-        <v>75.585477</v>
+      <c r="G250" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H250" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I250" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J250" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K250" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="L250" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M250" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N250" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O250" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L250" s="5" t="n">
+        <v>0.001511</v>
+      </c>
+      <c r="M250" s="5" t="n">
+        <v>0.000661</v>
+      </c>
+      <c r="N250" s="5" t="n">
+        <v>0.000282</v>
+      </c>
+      <c r="O250" s="5" t="n">
+        <v>0.000758</v>
       </c>
       <c r="P250" t="inlineStr">
         <is>
@@ -27304,15 +27138,19 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>Weighted Average Number of Shares Outstanding, Basic and</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>119,715 93,871 648,307 EQUITY 3,848,008 1,243,615 1,890,140 1,118,945</t>
-        </is>
-      </c>
-      <c r="D251" t="inlineStr"/>
+          <t>NET LOSS FOR THE YEAR</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E251" t="inlineStr">
         <is>
           <t>-</t>
@@ -27333,36 +27171,32 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I251" s="5" t="n">
-        <v>-2.454649</v>
-      </c>
-      <c r="J251" s="5" t="n">
-        <v>-3.321198</v>
+      <c r="I251" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J251" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K251" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="L251" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M251" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N251" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O251" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L251" s="5" t="n">
+        <v>-0.133977</v>
+      </c>
+      <c r="M251" s="5" t="n">
+        <v>-0.096067</v>
+      </c>
+      <c r="N251" s="5" t="n">
+        <v>-0.128842</v>
+      </c>
+      <c r="O251" s="5" t="n">
+        <v>-0.38283</v>
       </c>
       <c r="P251" t="inlineStr">
         <is>
@@ -27383,12 +27217,12 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>Weighted Average Number of Shares Outstanding, Basic and</t>
+          <t>OTHER COMPREHENSIVE GAIN (LOSS)</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Weighted Average Number of Shares Outstanding, Basic and total</t>
+          <t>Foreign Currency Translation Gain (Loss)</t>
         </is>
       </c>
       <c r="D252" t="inlineStr"/>
@@ -27437,15 +27271,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N252" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O252" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N252" s="5" t="n">
+        <v>0.00239</v>
+      </c>
+      <c r="O252" s="5" t="n">
+        <v>-0.012813</v>
       </c>
       <c r="P252" t="inlineStr">
         <is>
@@ -27466,15 +27296,19 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>Weighted Average Number of Shares Outstanding, Basic and</t>
+          <t>OTHER COMPREHENSIVE GAIN (LOSS)</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>DEFICIT (8,546,789) (3,321,198) (11,867,987)</t>
-        </is>
-      </c>
-      <c r="D253" t="inlineStr"/>
+          <t>NET COMPREHENSIVE LOSS FOR THE YEAR</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E253" t="inlineStr">
         <is>
           <t>-</t>
@@ -27495,11 +27329,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I253" s="5" t="n">
-        <v>-14.322636</v>
-      </c>
-      <c r="J253" s="5" t="n">
-        <v>-2.454649</v>
+      <c r="I253" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J253" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K253" t="inlineStr">
         <is>
@@ -27516,15 +27354,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N253" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O253" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N253" s="5" t="n">
+        <v>-0.126452</v>
+      </c>
+      <c r="O253" s="5" t="n">
+        <v>-0.395643</v>
       </c>
       <c r="P253" t="inlineStr">
         <is>
@@ -27543,13 +27377,21 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B254" t="inlineStr"/>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>OTHER COMPREHENSIVE GAIN (LOSS)</t>
+        </is>
+      </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Exploration Expenses (Note 5) $</t>
-        </is>
-      </c>
-      <c r="D254" t="inlineStr"/>
+          <t>BASIC AND DILUTED LOSS PER SHARE</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
       <c r="E254" t="inlineStr">
         <is>
           <t>-</t>
@@ -27560,14 +27402,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G254" s="5" t="n">
-        <v>0.648869</v>
-      </c>
-      <c r="H254" s="5" t="n">
-        <v>1.185129</v>
-      </c>
-      <c r="I254" s="5" t="n">
-        <v>1.754185</v>
+      <c r="G254" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H254" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I254" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J254" t="inlineStr">
         <is>
@@ -27589,15 +27437,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N254" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O254" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N254" s="5" t="n">
+        <v>-2e-09</v>
+      </c>
+      <c r="O254" s="5" t="n">
+        <v>-5e-09</v>
       </c>
       <c r="P254" t="inlineStr">
         <is>
@@ -27618,15 +27462,19 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>General and Administrative Expenses</t>
+          <t>OTHER COMPREHENSIVE GAIN (LOSS)</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Administrative fees and compensation (Note 8)</t>
-        </is>
-      </c>
-      <c r="D255" t="inlineStr"/>
+          <t>WEIGHTED AVERAGE NUMBER OF SHARES OUTSTANDING</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>BasicAverageShares</t>
+        </is>
+      </c>
       <c r="E255" t="inlineStr">
         <is>
           <t>-</t>
@@ -27642,11 +27490,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H255" s="5" t="n">
-        <v>0.240208</v>
-      </c>
-      <c r="I255" s="5" t="n">
-        <v>0.299304</v>
+      <c r="H255" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I255" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J255" t="inlineStr">
         <is>
@@ -27668,15 +27520,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N255" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O255" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N255" s="5" t="n">
+        <v>83.47251199999999</v>
+      </c>
+      <c r="O255" s="5" t="n">
+        <v>90.07525200000001</v>
       </c>
       <c r="P255" t="inlineStr">
         <is>
@@ -27697,15 +27545,19 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>General and Administrative Expenses</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Listing acquisition cost (Note 4)</t>
-        </is>
-      </c>
-      <c r="D256" t="inlineStr"/>
+          <t>LOSS BEFORE OTHER ITEMS</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>OperatingIncome</t>
+        </is>
+      </c>
       <c r="E256" t="inlineStr">
         <is>
           <t>-</t>
@@ -27721,8 +27573,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H256" s="5" t="n">
-        <v>0.720689</v>
+      <c r="H256" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I256" t="inlineStr">
         <is>
@@ -27739,20 +27593,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L256" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M256" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N256" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L256" s="5" t="n">
+        <v>-0.134033</v>
+      </c>
+      <c r="M256" s="5" t="n">
+        <v>-0.132499</v>
+      </c>
+      <c r="N256" s="5" t="n">
+        <v>-0.128842</v>
       </c>
       <c r="O256" t="inlineStr">
         <is>
@@ -27778,15 +27626,19 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>Other Expenses</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Impairment in advances to related party (Note 7)</t>
-        </is>
-      </c>
-      <c r="D257" t="inlineStr"/>
+          <t>Interest Income</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>InterestIncomeNonOperating</t>
+        </is>
+      </c>
       <c r="E257" t="inlineStr">
         <is>
           <t>-</t>
@@ -27802,8 +27654,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H257" s="5" t="n">
-        <v>-0.107514</v>
+      <c r="H257" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I257" t="inlineStr">
         <is>
@@ -27820,15 +27674,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L257" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M257" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L257" s="5" t="n">
+        <v>5.6e-05</v>
+      </c>
+      <c r="M257" s="5" t="n">
+        <v>9.3e-05</v>
       </c>
       <c r="N257" t="inlineStr">
         <is>
@@ -27859,19 +27709,15 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>Other Expenses</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Net Loss and Comprehensive Loss for the Year $</t>
-        </is>
-      </c>
-      <c r="D258" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Recovery of Colombia Sales Tax Receivable</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr"/>
       <c r="E258" t="inlineStr">
         <is>
           <t>-</t>
@@ -27882,14 +27728,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G258" s="5" t="n">
-        <v>-1.504812</v>
-      </c>
-      <c r="H258" s="5" t="n">
-        <v>-3.060595</v>
-      </c>
-      <c r="I258" s="5" t="n">
-        <v>-3.321198</v>
+      <c r="G258" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H258" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I258" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J258" t="inlineStr">
         <is>
@@ -27906,10 +27758,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M258" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M258" s="5" t="n">
+        <v>0.036339</v>
       </c>
       <c r="N258" t="inlineStr">
         <is>
@@ -27940,19 +27790,15 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>Other Expenses</t>
+          <t>OTHER COMPREHENSIVE LOSS</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Loss Per Share, Basic and diluted $</t>
-        </is>
-      </c>
-      <c r="D259" t="inlineStr">
-        <is>
-          <t>BasicEPS</t>
-        </is>
-      </c>
+          <t>Foreign Currency Translation Gain</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr"/>
       <c r="E259" t="inlineStr">
         <is>
           <t>-</t>
@@ -27963,14 +27809,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G259" s="5" t="n">
-        <v>-5e-08</v>
-      </c>
-      <c r="H259" s="5" t="n">
-        <v>-5e-08</v>
-      </c>
-      <c r="I259" s="5" t="n">
-        <v>-5e-08</v>
+      <c r="G259" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H259" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I259" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J259" t="inlineStr">
         <is>
@@ -27982,20 +27834,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L259" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M259" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N259" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L259" s="5" t="n">
+        <v>0.004293</v>
+      </c>
+      <c r="M259" s="5" t="n">
+        <v>0.011421</v>
+      </c>
+      <c r="N259" s="5" t="n">
+        <v>0.00239</v>
       </c>
       <c r="O259" t="inlineStr">
         <is>
@@ -28021,12 +27867,12 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>General And Administrative Expenses</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Administrative fees and compensation (Note 8)</t>
+          <t>Recovery of Columbia Sales Tax Receivable</t>
         </is>
       </c>
       <c r="D260" t="inlineStr"/>
@@ -28040,11 +27886,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G260" s="5" t="n">
-        <v>0.279249</v>
-      </c>
-      <c r="H260" s="5" t="n">
-        <v>0.240208</v>
+      <c r="G260" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H260" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I260" t="inlineStr">
         <is>
@@ -28066,10 +27916,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M260" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M260" s="5" t="n">
+        <v>0.036339</v>
       </c>
       <c r="N260" t="inlineStr">
         <is>
@@ -28098,21 +27946,13 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B261" t="inlineStr">
-        <is>
-          <t>General And Administrative Expenses</t>
-        </is>
-      </c>
+      <c r="B261" t="inlineStr"/>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Depreciation</t>
-        </is>
-      </c>
-      <c r="D261" t="inlineStr">
-        <is>
-          <t>Depreciation</t>
-        </is>
-      </c>
+          <t>Exploration Expenses (Note 4) $</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr"/>
       <c r="E261" t="inlineStr">
         <is>
           <t>-</t>
@@ -28123,21 +27963,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G261" s="5" t="n">
-        <v>0.045488</v>
-      </c>
-      <c r="H261" s="5" t="n">
-        <v>0.027694</v>
-      </c>
-      <c r="I261" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J261" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G261" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H261" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I261" s="5" t="n">
+        <v>1.754185</v>
+      </c>
+      <c r="J261" s="5" t="n">
+        <v>1.63686</v>
       </c>
       <c r="K261" t="inlineStr">
         <is>
@@ -28183,19 +28023,15 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>General And Administrative Expenses</t>
+          <t>General and Administrative Expenses</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Foreign exchange</t>
-        </is>
-      </c>
-      <c r="D262" t="inlineStr">
-        <is>
-          <t>ForeignExchangeTradingGains</t>
-        </is>
-      </c>
+          <t>Administrative fees and compensation (Note 6)</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr"/>
       <c r="E262" t="inlineStr">
         <is>
           <t>-</t>
@@ -28206,21 +28042,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G262" s="5" t="n">
-        <v>-0.004265</v>
-      </c>
-      <c r="H262" s="5" t="n">
-        <v>-0.006906</v>
-      </c>
-      <c r="I262" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J262" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G262" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H262" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I262" s="5" t="n">
+        <v>0.299304</v>
+      </c>
+      <c r="J262" s="5" t="n">
+        <v>0.313142</v>
       </c>
       <c r="K262" t="inlineStr">
         <is>
@@ -28266,15 +28102,19 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>General And Administrative Expenses</t>
+          <t>General and Administrative Expenses</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Legal, accounting and audit</t>
-        </is>
-      </c>
-      <c r="D263" t="inlineStr"/>
+          <t>Depreciation</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>Depreciation</t>
+        </is>
+      </c>
       <c r="E263" t="inlineStr">
         <is>
           <t>-</t>
@@ -28285,21 +28125,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G263" s="5" t="n">
-        <v>0.240466</v>
+      <c r="G263" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H263" s="5" t="n">
-        <v>0.48218</v>
-      </c>
-      <c r="I263" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J263" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.027694</v>
+      </c>
+      <c r="I263" s="5" t="n">
+        <v>0.003542</v>
+      </c>
+      <c r="J263" s="5" t="n">
+        <v>0.005686</v>
       </c>
       <c r="K263" t="inlineStr">
         <is>
@@ -28345,15 +28183,19 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>General And Administrative Expenses</t>
+          <t>General and Administrative Expenses</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Listing acquisition cost (Note 4)</t>
-        </is>
-      </c>
-      <c r="D264" t="inlineStr"/>
+          <t>Foreign exchange</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>ForeignExchangeTradingGains</t>
+        </is>
+      </c>
       <c r="E264" t="inlineStr">
         <is>
           <t>-</t>
@@ -28370,17 +28212,13 @@
         </is>
       </c>
       <c r="H264" s="5" t="n">
-        <v>0.720689</v>
-      </c>
-      <c r="I264" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J264" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.006906</v>
+      </c>
+      <c r="I264" s="5" t="n">
+        <v>0.01266</v>
+      </c>
+      <c r="J264" s="5" t="n">
+        <v>-0.007856</v>
       </c>
       <c r="K264" t="inlineStr">
         <is>
@@ -28426,12 +28264,12 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>General And Administrative Expenses</t>
+          <t>General and Administrative Expenses</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>Office and sundry</t>
+          <t>Legal, accounting and audit</t>
         </is>
       </c>
       <c r="D265" t="inlineStr"/>
@@ -28445,21 +28283,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G265" s="5" t="n">
-        <v>0.12745</v>
+      <c r="G265" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H265" s="5" t="n">
-        <v>0.178829</v>
-      </c>
-      <c r="I265" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J265" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.48218</v>
+      </c>
+      <c r="I265" s="5" t="n">
+        <v>0.348285</v>
+      </c>
+      <c r="J265" s="5" t="n">
+        <v>0.137853</v>
       </c>
       <c r="K265" t="inlineStr">
         <is>
@@ -28505,12 +28341,12 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>General And Administrative Expenses</t>
+          <t>General and Administrative Expenses</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Telecommunications</t>
+          <t>Office and sundry</t>
         </is>
       </c>
       <c r="D266" t="inlineStr"/>
@@ -28524,21 +28360,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G266" s="5" t="n">
-        <v>0.050871</v>
+      <c r="G266" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H266" s="5" t="n">
-        <v>0.034108</v>
-      </c>
-      <c r="I266" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J266" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.178829</v>
+      </c>
+      <c r="I266" s="5" t="n">
+        <v>0.201335</v>
+      </c>
+      <c r="J266" s="5" t="n">
+        <v>0.185196</v>
       </c>
       <c r="K266" t="inlineStr">
         <is>
@@ -28584,19 +28418,15 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>General And Administrative Expenses</t>
+          <t>General and Administrative Expenses</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>Travel</t>
-        </is>
-      </c>
-      <c r="D267" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
+          <t>Share-based compensation</t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr"/>
       <c r="E267" t="inlineStr">
         <is>
           <t>-</t>
@@ -28607,21 +28437,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G267" s="5" t="n">
-        <v>0.016685</v>
-      </c>
-      <c r="H267" s="5" t="n">
-        <v>0.09114999999999999</v>
-      </c>
-      <c r="I267" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J267" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G267" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H267" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I267" s="5" t="n">
+        <v>0.643169</v>
+      </c>
+      <c r="J267" s="5" t="n">
+        <v>0.032109</v>
       </c>
       <c r="K267" t="inlineStr">
         <is>
@@ -28667,19 +28497,15 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>General And Administrative Expenses</t>
+          <t>General and Administrative Expenses</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Total General And Administrative Expenses</t>
-        </is>
-      </c>
-      <c r="D268" t="inlineStr">
-        <is>
-          <t>GeneralAndAdministrativeExpense</t>
-        </is>
-      </c>
+          <t>Telecommunications</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr"/>
       <c r="E268" t="inlineStr">
         <is>
           <t>-</t>
@@ -28690,21 +28516,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G268" s="5" t="n">
-        <v>0.7559439999999999</v>
+      <c r="G268" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H268" s="5" t="n">
-        <v>1.767952</v>
-      </c>
-      <c r="I268" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J268" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.034108</v>
+      </c>
+      <c r="I268" s="5" t="n">
+        <v>0.027074</v>
+      </c>
+      <c r="J268" s="5" t="n">
+        <v>0.027959</v>
       </c>
       <c r="K268" t="inlineStr">
         <is>
@@ -28750,15 +28574,19 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>General And Administrative Expenses</t>
+          <t>General and Administrative Expenses</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>Net Loss Before Other Expenses</t>
-        </is>
-      </c>
-      <c r="D269" t="inlineStr"/>
+          <t>Travel</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E269" t="inlineStr">
         <is>
           <t>-</t>
@@ -28769,21 +28597,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G269" s="5" t="n">
-        <v>-1.404813</v>
+      <c r="G269" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H269" s="5" t="n">
-        <v>-2.953081</v>
-      </c>
-      <c r="I269" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J269" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.09114999999999999</v>
+      </c>
+      <c r="I269" s="5" t="n">
+        <v>0.031644</v>
+      </c>
+      <c r="J269" s="5" t="n">
+        <v>0.1237</v>
       </c>
       <c r="K269" t="inlineStr">
         <is>
@@ -28829,15 +28655,19 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>Other Expenses</t>
+          <t>General and Administrative Expenses</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Impairment in value of long term investment (Note 7)</t>
-        </is>
-      </c>
-      <c r="D270" t="inlineStr"/>
+          <t>Total General And Administrative Expenses</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>GeneralAndAdministrativeExpense</t>
+        </is>
+      </c>
       <c r="E270" t="inlineStr">
         <is>
           <t>-</t>
@@ -28848,23 +28678,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G270" s="5" t="n">
-        <v>-0.099999</v>
-      </c>
-      <c r="H270" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I270" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J270" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G270" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H270" s="5" t="n">
+        <v>1.767952</v>
+      </c>
+      <c r="I270" s="5" t="n">
+        <v>1.567013</v>
+      </c>
+      <c r="J270" s="5" t="n">
+        <v>0.817789</v>
       </c>
       <c r="K270" t="inlineStr">
         <is>
@@ -28910,12 +28736,12 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>Weighted Average Number of Shares Outstanding, Basic and</t>
+          <t>General and Administrative Expenses</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>- - 387,410 - - - DEFICIT (4,368,792) (1,504,812) (5,873,604)</t>
+          <t>Net Loss Before Other Expenses</t>
         </is>
       </c>
       <c r="D271" t="inlineStr"/>
@@ -28929,21 +28755,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G271" s="5" t="n">
-        <v>-8.546789</v>
+      <c r="G271" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H271" s="5" t="n">
-        <v>-3.060595</v>
-      </c>
-      <c r="I271" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J271" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-2.953081</v>
+      </c>
+      <c r="I271" s="5" t="n">
+        <v>-3.321198</v>
+      </c>
+      <c r="J271" s="5" t="n">
+        <v>-2.454649</v>
       </c>
       <c r="K271" t="inlineStr">
         <is>
@@ -28989,76 +28813,3867 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
+          <t>General and Administrative Expenses</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>Net Loss and Comprehensive Loss for the Year $</t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E272" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F272" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G272" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H272" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I272" s="5" t="n">
+        <v>-3.321198</v>
+      </c>
+      <c r="J272" s="5" t="n">
+        <v>-2.454649</v>
+      </c>
+      <c r="K272" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L272" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M272" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N272" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O272" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P272" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q272" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>General and Administrative Expenses</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>Loss Per Share, Basic and diluted $</t>
+        </is>
+      </c>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
+      <c r="E273" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F273" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G273" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H273" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I273" s="5" t="n">
+        <v>-5e-08</v>
+      </c>
+      <c r="J273" s="5" t="n">
+        <v>-3e-08</v>
+      </c>
+      <c r="K273" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L273" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M273" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N273" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O273" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P273" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q273" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>Weighted Average Number of Shares Outstanding, Basic and</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>Weighted Average Number of Shares Outstanding, Basic and diluted</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr"/>
+      <c r="E274" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F274" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G274" s="5" t="n">
+        <v>31.509819</v>
+      </c>
+      <c r="H274" s="5" t="n">
+        <v>60.418467</v>
+      </c>
+      <c r="I274" s="5" t="n">
+        <v>72.793398</v>
+      </c>
+      <c r="J274" s="5" t="n">
+        <v>75.585477</v>
+      </c>
+      <c r="K274" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L274" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M274" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N274" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O274" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P274" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q274" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>Weighted Average Number of Shares Outstanding, Basic and</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>119,715 93,871 648,307 EQUITY 3,848,008 1,243,615 1,890,140 1,118,945</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr"/>
+      <c r="E275" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F275" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G275" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H275" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I275" s="5" t="n">
+        <v>-2.454649</v>
+      </c>
+      <c r="J275" s="5" t="n">
+        <v>-3.321198</v>
+      </c>
+      <c r="K275" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L275" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M275" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N275" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O275" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P275" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q275" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>Weighted Average Number of Shares Outstanding, Basic and</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>Weighted Average Number of Shares Outstanding, Basic and total</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr"/>
+      <c r="E276" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F276" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G276" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H276" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I276" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J276" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K276" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L276" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M276" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N276" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O276" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P276" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q276" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>Weighted Average Number of Shares Outstanding, Basic and</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>DEFICIT (8,546,789) (3,321,198) (11,867,987)</t>
+        </is>
+      </c>
+      <c r="D277" t="inlineStr"/>
+      <c r="E277" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F277" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G277" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H277" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I277" s="5" t="n">
+        <v>-14.322636</v>
+      </c>
+      <c r="J277" s="5" t="n">
+        <v>-2.454649</v>
+      </c>
+      <c r="K277" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L277" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M277" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N277" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O277" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P277" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q277" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr"/>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>Exploration Expenses (Note 5) $</t>
+        </is>
+      </c>
+      <c r="D278" t="inlineStr"/>
+      <c r="E278" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F278" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G278" s="5" t="n">
+        <v>0.648869</v>
+      </c>
+      <c r="H278" s="5" t="n">
+        <v>1.185129</v>
+      </c>
+      <c r="I278" s="5" t="n">
+        <v>1.754185</v>
+      </c>
+      <c r="J278" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K278" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L278" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M278" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N278" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O278" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P278" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q278" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>General and Administrative Expenses</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>Administrative fees and compensation (Note 8)</t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr"/>
+      <c r="E279" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F279" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G279" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H279" s="5" t="n">
+        <v>0.240208</v>
+      </c>
+      <c r="I279" s="5" t="n">
+        <v>0.299304</v>
+      </c>
+      <c r="J279" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K279" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L279" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M279" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N279" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O279" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P279" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q279" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>General and Administrative Expenses</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>Listing acquisition cost (Note 4)</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr"/>
+      <c r="E280" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F280" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G280" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H280" s="5" t="n">
+        <v>0.720689</v>
+      </c>
+      <c r="I280" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J280" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K280" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L280" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M280" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N280" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O280" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P280" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q280" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>Other Expenses</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>Impairment in advances to related party (Note 7)</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr"/>
+      <c r="E281" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F281" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G281" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H281" s="5" t="n">
+        <v>-0.107514</v>
+      </c>
+      <c r="I281" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J281" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K281" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L281" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M281" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N281" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O281" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P281" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q281" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>Other Expenses</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>Net Loss and Comprehensive Loss for the Year $</t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E282" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F282" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G282" s="5" t="n">
+        <v>-1.504812</v>
+      </c>
+      <c r="H282" s="5" t="n">
+        <v>-3.060595</v>
+      </c>
+      <c r="I282" s="5" t="n">
+        <v>-3.321198</v>
+      </c>
+      <c r="J282" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K282" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L282" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M282" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N282" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O282" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P282" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q282" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>Other Expenses</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>Loss Per Share, Basic and diluted $</t>
+        </is>
+      </c>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
+      <c r="E283" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F283" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G283" s="5" t="n">
+        <v>-5e-08</v>
+      </c>
+      <c r="H283" s="5" t="n">
+        <v>-5e-08</v>
+      </c>
+      <c r="I283" s="5" t="n">
+        <v>-5e-08</v>
+      </c>
+      <c r="J283" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K283" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L283" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M283" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N283" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O283" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P283" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q283" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>General And Administrative Expenses</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>Administrative fees and compensation (Note 8)</t>
+        </is>
+      </c>
+      <c r="D284" t="inlineStr"/>
+      <c r="E284" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F284" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G284" s="5" t="n">
+        <v>0.279249</v>
+      </c>
+      <c r="H284" s="5" t="n">
+        <v>0.240208</v>
+      </c>
+      <c r="I284" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J284" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K284" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L284" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M284" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N284" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O284" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P284" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q284" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>General And Administrative Expenses</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>Depreciation</t>
+        </is>
+      </c>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>Depreciation</t>
+        </is>
+      </c>
+      <c r="E285" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F285" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G285" s="5" t="n">
+        <v>0.045488</v>
+      </c>
+      <c r="H285" s="5" t="n">
+        <v>0.027694</v>
+      </c>
+      <c r="I285" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J285" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K285" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L285" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M285" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N285" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O285" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P285" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q285" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>General And Administrative Expenses</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>Foreign exchange</t>
+        </is>
+      </c>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t>ForeignExchangeTradingGains</t>
+        </is>
+      </c>
+      <c r="E286" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F286" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G286" s="5" t="n">
+        <v>-0.004265</v>
+      </c>
+      <c r="H286" s="5" t="n">
+        <v>-0.006906</v>
+      </c>
+      <c r="I286" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J286" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K286" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L286" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M286" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N286" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O286" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P286" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q286" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>General And Administrative Expenses</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>Legal, accounting and audit</t>
+        </is>
+      </c>
+      <c r="D287" t="inlineStr"/>
+      <c r="E287" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F287" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G287" s="5" t="n">
+        <v>0.240466</v>
+      </c>
+      <c r="H287" s="5" t="n">
+        <v>0.48218</v>
+      </c>
+      <c r="I287" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J287" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K287" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L287" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M287" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N287" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O287" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P287" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q287" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>General And Administrative Expenses</t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>Listing acquisition cost (Note 4)</t>
+        </is>
+      </c>
+      <c r="D288" t="inlineStr"/>
+      <c r="E288" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F288" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G288" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H288" s="5" t="n">
+        <v>0.720689</v>
+      </c>
+      <c r="I288" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J288" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K288" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L288" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M288" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N288" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O288" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P288" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q288" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>General And Administrative Expenses</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>Office and sundry</t>
+        </is>
+      </c>
+      <c r="D289" t="inlineStr"/>
+      <c r="E289" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F289" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G289" s="5" t="n">
+        <v>0.12745</v>
+      </c>
+      <c r="H289" s="5" t="n">
+        <v>0.178829</v>
+      </c>
+      <c r="I289" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J289" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K289" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L289" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M289" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N289" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O289" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P289" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q289" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>General And Administrative Expenses</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>Telecommunications</t>
+        </is>
+      </c>
+      <c r="D290" t="inlineStr"/>
+      <c r="E290" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F290" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G290" s="5" t="n">
+        <v>0.050871</v>
+      </c>
+      <c r="H290" s="5" t="n">
+        <v>0.034108</v>
+      </c>
+      <c r="I290" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J290" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K290" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L290" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M290" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N290" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O290" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P290" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q290" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>General And Administrative Expenses</t>
+        </is>
+      </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>Travel</t>
+        </is>
+      </c>
+      <c r="D291" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E291" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F291" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G291" s="5" t="n">
+        <v>0.016685</v>
+      </c>
+      <c r="H291" s="5" t="n">
+        <v>0.09114999999999999</v>
+      </c>
+      <c r="I291" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J291" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K291" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L291" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M291" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N291" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O291" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P291" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q291" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>General And Administrative Expenses</t>
+        </is>
+      </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>Total General And Administrative Expenses</t>
+        </is>
+      </c>
+      <c r="D292" t="inlineStr">
+        <is>
+          <t>GeneralAndAdministrativeExpense</t>
+        </is>
+      </c>
+      <c r="E292" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F292" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G292" s="5" t="n">
+        <v>0.7559439999999999</v>
+      </c>
+      <c r="H292" s="5" t="n">
+        <v>1.767952</v>
+      </c>
+      <c r="I292" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J292" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K292" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L292" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M292" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N292" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O292" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P292" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q292" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>General And Administrative Expenses</t>
+        </is>
+      </c>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>Net Loss Before Other Expenses</t>
+        </is>
+      </c>
+      <c r="D293" t="inlineStr"/>
+      <c r="E293" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F293" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G293" s="5" t="n">
+        <v>-1.404813</v>
+      </c>
+      <c r="H293" s="5" t="n">
+        <v>-2.953081</v>
+      </c>
+      <c r="I293" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J293" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K293" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L293" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M293" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N293" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O293" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P293" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q293" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>Other Expenses</t>
+        </is>
+      </c>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>Impairment in value of long term investment (Note 7)</t>
+        </is>
+      </c>
+      <c r="D294" t="inlineStr"/>
+      <c r="E294" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F294" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G294" s="5" t="n">
+        <v>-0.099999</v>
+      </c>
+      <c r="H294" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I294" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J294" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K294" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L294" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M294" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N294" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O294" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P294" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q294" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>Weighted Average Number of Shares Outstanding, Basic and</t>
+        </is>
+      </c>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t>- - 387,410 - - - DEFICIT (4,368,792) (1,504,812) (5,873,604)</t>
+        </is>
+      </c>
+      <c r="D295" t="inlineStr"/>
+      <c r="E295" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F295" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G295" s="5" t="n">
+        <v>-8.546789</v>
+      </c>
+      <c r="H295" s="5" t="n">
+        <v>-3.060595</v>
+      </c>
+      <c r="I295" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J295" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K295" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L295" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M295" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N295" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O295" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P295" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q295" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
           <t>statements.</t>
         </is>
       </c>
-      <c r="C272" t="inlineStr">
+      <c r="C296" t="inlineStr">
         <is>
           <t>statements.</t>
         </is>
       </c>
-      <c r="D272" t="inlineStr"/>
-      <c r="E272" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F272" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G272" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H272" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I272" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J272" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K272" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L272" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M272" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N272" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O272" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P272" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q272" t="inlineStr">
+      <c r="D296" t="inlineStr"/>
+      <c r="E296" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F296" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G296" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H296" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I296" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J296" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K296" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L296" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M296" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N296" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O296" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P296" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q296" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>EXPLORATION EXPENSES</t>
+        </is>
+      </c>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t>TARAIRA GOLD BELT, COLOMBIA ADVANCES (NOTE 5) $</t>
+        </is>
+      </c>
+      <c r="D297" t="inlineStr"/>
+      <c r="E297" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F297" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G297" s="5" t="n">
+        <v>0.38741</v>
+      </c>
+      <c r="H297" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I297" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J297" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K297" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L297" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M297" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N297" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O297" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P297" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q297" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>EXPLORATION EXPENSES</t>
+        </is>
+      </c>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>OTHER EXPLORATION COSTS</t>
+        </is>
+      </c>
+      <c r="D298" t="inlineStr"/>
+      <c r="E298" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F298" s="5" t="n">
+        <v>0.002505</v>
+      </c>
+      <c r="G298" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H298" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I298" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J298" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K298" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L298" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M298" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N298" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O298" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P298" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q298" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>EXPLORATION EXPENSES</t>
+        </is>
+      </c>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t>EXPLORATION EXPENSES total</t>
+        </is>
+      </c>
+      <c r="D299" t="inlineStr">
+        <is>
+          <t>OperatingExpense</t>
+        </is>
+      </c>
+      <c r="E299" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F299" s="5" t="n">
+        <v>0.002505</v>
+      </c>
+      <c r="G299" s="5" t="n">
+        <v>0.38741</v>
+      </c>
+      <c r="H299" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I299" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J299" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K299" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L299" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M299" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N299" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O299" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P299" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q299" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>ADMINISTRATION EXPENSES</t>
+        </is>
+      </c>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>CONSULTING FEES</t>
+        </is>
+      </c>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E300" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F300" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G300" s="5" t="n">
+        <v>0.059651</v>
+      </c>
+      <c r="H300" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I300" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J300" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K300" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L300" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M300" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N300" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O300" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P300" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q300" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>ADMINISTRATION EXPENSES</t>
+        </is>
+      </c>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t>FOREIGN EXCHANGE LOSS (GAIN)</t>
+        </is>
+      </c>
+      <c r="D301" t="inlineStr">
+        <is>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
+      <c r="E301" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F301" s="5" t="n">
+        <v>7.499999999999999e-05</v>
+      </c>
+      <c r="G301" s="5" t="n">
+        <v>-0.00116</v>
+      </c>
+      <c r="H301" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I301" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J301" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K301" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L301" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M301" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N301" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O301" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P301" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q301" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>ADMINISTRATION EXPENSES</t>
+        </is>
+      </c>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t>OFFICE AND MISCELLANEOUS</t>
+        </is>
+      </c>
+      <c r="D302" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E302" s="5" t="n">
+        <v>0.007006</v>
+      </c>
+      <c r="F302" s="5" t="n">
+        <v>0.006486</v>
+      </c>
+      <c r="G302" s="5" t="n">
+        <v>0.010189</v>
+      </c>
+      <c r="H302" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I302" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J302" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K302" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L302" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M302" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N302" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O302" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P302" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q302" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>ADMINISTRATION EXPENSES</t>
+        </is>
+      </c>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t>PROFESSIONAL FEES</t>
+        </is>
+      </c>
+      <c r="D303" t="inlineStr">
+        <is>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
+        </is>
+      </c>
+      <c r="E303" s="5" t="n">
+        <v>0.032387</v>
+      </c>
+      <c r="F303" s="5" t="n">
+        <v>0.040593</v>
+      </c>
+      <c r="G303" s="5" t="n">
+        <v>0.051897</v>
+      </c>
+      <c r="H303" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I303" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J303" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K303" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L303" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M303" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N303" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O303" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P303" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q303" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>ADMINISTRATION EXPENSES</t>
+        </is>
+      </c>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t>RENT (NOTE 6)</t>
+        </is>
+      </c>
+      <c r="D304" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E304" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F304" s="5" t="n">
+        <v>0.02306</v>
+      </c>
+      <c r="G304" s="5" t="n">
+        <v>0.017338</v>
+      </c>
+      <c r="H304" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I304" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J304" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K304" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L304" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M304" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N304" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O304" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P304" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q304" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>ADMINISTRATION EXPENSES</t>
+        </is>
+      </c>
+      <c r="C305" t="inlineStr">
+        <is>
+          <t>SECRETARIAL (NOTE 6)</t>
+        </is>
+      </c>
+      <c r="D305" t="inlineStr"/>
+      <c r="E305" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F305" s="5" t="n">
+        <v>0.040317</v>
+      </c>
+      <c r="G305" s="5" t="n">
+        <v>0.043506</v>
+      </c>
+      <c r="H305" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I305" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J305" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K305" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L305" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M305" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N305" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O305" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P305" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q305" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>ADMINISTRATION EXPENSES</t>
+        </is>
+      </c>
+      <c r="C306" t="inlineStr">
+        <is>
+          <t>STOCK EXCHANGE AND FILING FEES</t>
+        </is>
+      </c>
+      <c r="D306" t="inlineStr"/>
+      <c r="E306" s="5" t="n">
+        <v>0.008976</v>
+      </c>
+      <c r="F306" s="5" t="n">
+        <v>0.010062</v>
+      </c>
+      <c r="G306" s="5" t="n">
+        <v>0.019652</v>
+      </c>
+      <c r="H306" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I306" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J306" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K306" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L306" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M306" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N306" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O306" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P306" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q306" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>ADMINISTRATION EXPENSES</t>
+        </is>
+      </c>
+      <c r="C307" t="inlineStr">
+        <is>
+          <t>STOCK-BASED COMPENSATION (NOTE 7)</t>
+        </is>
+      </c>
+      <c r="D307" t="inlineStr"/>
+      <c r="E307" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F307" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G307" s="5" t="n">
+        <v>0.71292</v>
+      </c>
+      <c r="H307" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I307" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J307" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K307" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L307" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M307" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N307" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O307" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P307" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q307" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>ADMINISTRATION EXPENSES</t>
+        </is>
+      </c>
+      <c r="C308" t="inlineStr">
+        <is>
+          <t>TRANSFER AGENT FEES</t>
+        </is>
+      </c>
+      <c r="D308" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E308" s="5" t="n">
+        <v>0.010168</v>
+      </c>
+      <c r="F308" s="5" t="n">
+        <v>0.011864</v>
+      </c>
+      <c r="G308" s="5" t="n">
+        <v>0.011515</v>
+      </c>
+      <c r="H308" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I308" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J308" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K308" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L308" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M308" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N308" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O308" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P308" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q308" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>ADMINISTRATION EXPENSES</t>
+        </is>
+      </c>
+      <c r="C309" t="inlineStr">
+        <is>
+          <t>TRAVEL AND PROMOTION</t>
+        </is>
+      </c>
+      <c r="D309" t="inlineStr">
+        <is>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
+      <c r="E309" s="5" t="n">
+        <v>0.019162</v>
+      </c>
+      <c r="F309" s="5" t="n">
+        <v>0.019037</v>
+      </c>
+      <c r="G309" s="5" t="n">
+        <v>0.029687</v>
+      </c>
+      <c r="H309" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I309" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J309" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K309" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L309" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M309" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N309" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O309" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P309" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q309" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>ADMINISTRATION EXPENSES</t>
+        </is>
+      </c>
+      <c r="C310" t="inlineStr">
+        <is>
+          <t>INTEREST INCOME</t>
+        </is>
+      </c>
+      <c r="D310" t="inlineStr">
+        <is>
+          <t>InterestIncomeNonOperating</t>
+        </is>
+      </c>
+      <c r="E310" s="5" t="n">
+        <v>-0.007441</v>
+      </c>
+      <c r="F310" s="5" t="n">
+        <v>-0.002065</v>
+      </c>
+      <c r="G310" s="5" t="n">
+        <v>-1e-05</v>
+      </c>
+      <c r="H310" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I310" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J310" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K310" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L310" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M310" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N310" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O310" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P310" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q310" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>ADMINISTRATION EXPENSES</t>
+        </is>
+      </c>
+      <c r="C311" t="inlineStr">
+        <is>
+          <t>ADMINISTRATION EXPENSES total</t>
+        </is>
+      </c>
+      <c r="D311" t="inlineStr">
+        <is>
+          <t>OperatingExpense</t>
+        </is>
+      </c>
+      <c r="E311" s="5" t="n">
+        <v>0.132435</v>
+      </c>
+      <c r="F311" s="5" t="n">
+        <v>0.149429</v>
+      </c>
+      <c r="G311" s="5" t="n">
+        <v>0.955185</v>
+      </c>
+      <c r="H311" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I311" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J311" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K311" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L311" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M311" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N311" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O311" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P311" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q311" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>NET LOSS AND</t>
+        </is>
+      </c>
+      <c r="C312" t="inlineStr">
+        <is>
+          <t>COMPREHENSIVE LOSS FOR THE YEAR $</t>
+        </is>
+      </c>
+      <c r="D312" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E312" s="5" t="n">
+        <v>-0.118876</v>
+      </c>
+      <c r="F312" s="5" t="n">
+        <v>-0.151934</v>
+      </c>
+      <c r="G312" s="5" t="n">
+        <v>-1.342595</v>
+      </c>
+      <c r="H312" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I312" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J312" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K312" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L312" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M312" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N312" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O312" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P312" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q312" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>BASIC AND FULLY DILUTED</t>
+        </is>
+      </c>
+      <c r="C313" t="inlineStr">
+        <is>
+          <t>LOSS PER COMMON SHARE $</t>
+        </is>
+      </c>
+      <c r="D313" t="inlineStr"/>
+      <c r="E313" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F313" s="5" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="G313" s="5" t="n">
+        <v>2e-08</v>
+      </c>
+      <c r="H313" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I313" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J313" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K313" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L313" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M313" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N313" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O313" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P313" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q313" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>WEIGHTED AVERAGE NUMBER OF COMMON</t>
+        </is>
+      </c>
+      <c r="C314" t="inlineStr">
+        <is>
+          <t>SHARES OUTSTANDING</t>
+        </is>
+      </c>
+      <c r="D314" t="inlineStr">
+        <is>
+          <t>SharesOutstanding</t>
+        </is>
+      </c>
+      <c r="E314" s="5" t="n">
+        <v>27.860543</v>
+      </c>
+      <c r="F314" s="5" t="n">
+        <v>28.613452</v>
+      </c>
+      <c r="G314" s="5" t="n">
+        <v>55.96584</v>
+      </c>
+      <c r="H314" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I314" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J314" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K314" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L314" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M314" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N314" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O314" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P314" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q314" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>EXPLORATION EXPENSES</t>
+        </is>
+      </c>
+      <c r="C315" t="inlineStr">
+        <is>
+          <t>EXPLORATION COSTS (RECOVERIES) $</t>
+        </is>
+      </c>
+      <c r="D315" t="inlineStr"/>
+      <c r="E315" s="5" t="n">
+        <v>-0.013559</v>
+      </c>
+      <c r="F315" s="5" t="n">
+        <v>0.002505</v>
+      </c>
+      <c r="G315" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H315" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I315" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J315" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K315" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L315" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M315" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N315" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O315" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P315" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q315" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>ADMINISTRATION EXPENSES</t>
+        </is>
+      </c>
+      <c r="C316" t="inlineStr">
+        <is>
+          <t>RENT</t>
+        </is>
+      </c>
+      <c r="D316" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E316" s="5" t="n">
+        <v>0.019989</v>
+      </c>
+      <c r="F316" s="5" t="n">
+        <v>0.02306</v>
+      </c>
+      <c r="G316" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H316" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I316" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J316" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K316" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L316" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M316" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N316" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O316" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P316" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q316" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>ADMINISTRATION EXPENSES</t>
+        </is>
+      </c>
+      <c r="C317" t="inlineStr">
+        <is>
+          <t>SECRETARIAL</t>
+        </is>
+      </c>
+      <c r="D317" t="inlineStr"/>
+      <c r="E317" s="5" t="n">
+        <v>0.042188</v>
+      </c>
+      <c r="F317" s="5" t="n">
+        <v>0.040317</v>
+      </c>
+      <c r="G317" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H317" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I317" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J317" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K317" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L317" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M317" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N317" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O317" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P317" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q317" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>ADMINISTRATION EXPENSES</t>
+        </is>
+      </c>
+      <c r="C318" t="inlineStr">
+        <is>
+          <t>FOREIGN EXCHANGE LOSS</t>
+        </is>
+      </c>
+      <c r="D318" t="inlineStr">
+        <is>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
+      <c r="E318" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F318" s="5" t="n">
+        <v>7.499999999999999e-05</v>
+      </c>
+      <c r="G318" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H318" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I318" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J318" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K318" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L318" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M318" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N318" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O318" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P318" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q318" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>BASIC AND FULLY DILUTED</t>
+        </is>
+      </c>
+      <c r="C319" t="inlineStr">
+        <is>
+          <t>NET LOSS PER COMMON SHARE $</t>
+        </is>
+      </c>
+      <c r="D319" t="inlineStr"/>
+      <c r="E319" s="5" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="F319" s="5" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="G319" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H319" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I319" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J319" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K319" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L319" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M319" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N319" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O319" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P319" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q319" t="inlineStr">
         <is>
           <t>-</t>
         </is>
